--- a/docs/exports/financials_extracted.xlsx
+++ b/docs/exports/financials_extracted.xlsx
@@ -1354,10 +1354,16 @@
       <c r="J2" t="b">
         <v>0</v>
       </c>
+      <c r="K2" t="n">
+        <v>73000</v>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0479</v>
       </c>
       <c r="N2" t="n">
         <v>0.6841</v>
@@ -1508,6 +1514,22 @@
       <c r="BK2" t="inlineStr">
         <is>
           <t>assumed 100% parent NP (no NCI attribution row found)</t>
+        </is>
+      </c>
+      <c r="CP2" t="n">
+        <v>73000</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>47</v>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>Long term loans</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>high</t>
         </is>
       </c>
       <c r="EI2" t="n">
@@ -1566,10 +1588,16 @@
       <c r="J3" t="b">
         <v>0</v>
       </c>
+      <c r="K3" t="n">
+        <v>73000</v>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0488</v>
       </c>
       <c r="N3" t="n">
         <v>0.5435</v>
@@ -1738,6 +1766,22 @@
       <c r="BZ3" t="inlineStr">
         <is>
           <t>label found but no number extracted</t>
+        </is>
+      </c>
+      <c r="CP3" t="n">
+        <v>73000</v>
+      </c>
+      <c r="CQ3" t="n">
+        <v>26</v>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>Long term loans</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
+          <t>high</t>
         </is>
       </c>
       <c r="EI3" t="n">
@@ -1796,10 +1840,16 @@
       <c r="J4" t="b">
         <v>0</v>
       </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>zero</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0.6655</v>
@@ -1976,6 +2026,24 @@
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
+        <is>
+          <t>label found but no number extracted</t>
+        </is>
+      </c>
+      <c r="CQ4" t="n">
+        <v>62</v>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>Long term loans</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="CT4" t="inlineStr">
         <is>
           <t>label found but no number extracted</t>
         </is>
@@ -2036,10 +2104,16 @@
       <c r="J5" t="b">
         <v>0</v>
       </c>
+      <c r="K5" t="n">
+        <v>458401</v>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0.3375</v>
       </c>
       <c r="N5" t="n">
         <v>0.7752</v>
@@ -2213,6 +2287,22 @@
       <c r="BZ5" t="inlineStr">
         <is>
           <t>label found but no number extracted</t>
+        </is>
+      </c>
+      <c r="CP5" t="n">
+        <v>458401</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>54</v>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>Long term loans</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
+        <is>
+          <t>high</t>
         </is>
       </c>
       <c r="EI5" t="n">
@@ -2266,10 +2356,16 @@
       <c r="J6" t="b">
         <v>0</v>
       </c>
+      <c r="K6" t="n">
+        <v>2662665</v>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1.9398</v>
       </c>
       <c r="N6" t="n">
         <v>0.7992</v>
@@ -2438,6 +2534,22 @@
       <c r="BZ6" t="inlineStr">
         <is>
           <t>label found but no number extracted</t>
+        </is>
+      </c>
+      <c r="CP6" t="n">
+        <v>2662665</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>57</v>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>Long term loans</t>
+        </is>
+      </c>
+      <c r="CS6" t="inlineStr">
+        <is>
+          <t>high</t>
         </is>
       </c>
       <c r="EI6" t="n">
@@ -2496,10 +2608,16 @@
       <c r="J7" t="b">
         <v>0</v>
       </c>
+      <c r="K7" t="n">
+        <v>2612041</v>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>2.1294</v>
       </c>
       <c r="N7" t="n">
         <v>0.8338</v>
@@ -2668,6 +2786,22 @@
       <c r="BZ7" t="inlineStr">
         <is>
           <t>label found but no number extracted</t>
+        </is>
+      </c>
+      <c r="CP7" t="n">
+        <v>2612041</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>65</v>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>Long term loans</t>
+        </is>
+      </c>
+      <c r="CS7" t="inlineStr">
+        <is>
+          <t>high</t>
         </is>
       </c>
       <c r="EI7" t="n">
@@ -4304,7 +4438,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>27641</v>
+        <v>28953</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -4312,7 +4446,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.2458</v>
+        <v>0.2575</v>
       </c>
       <c r="N14" t="n">
         <v>0.6294999999999999</v>
@@ -4478,6 +4612,22 @@
         </is>
       </c>
       <c r="CN14" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CP14" t="n">
+        <v>1312</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>54</v>
+      </c>
+      <c r="CR14" t="inlineStr">
+        <is>
+          <t>Islamic loans</t>
+        </is>
+      </c>
+      <c r="CS14" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -4539,7 +4689,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>25355</v>
+        <v>26659</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -4547,7 +4697,7 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.2255</v>
+        <v>0.2371</v>
       </c>
       <c r="N15" t="n">
         <v>0.5938</v>
@@ -4713,6 +4863,22 @@
         </is>
       </c>
       <c r="CN15" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CP15" t="n">
+        <v>1304</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>92</v>
+      </c>
+      <c r="CR15" t="inlineStr">
+        <is>
+          <t>Islamic loans</t>
+        </is>
+      </c>
+      <c r="CS15" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -4774,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1098</v>
+        <v>2428</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -4782,7 +4948,7 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.0098</v>
+        <v>0.0216</v>
       </c>
       <c r="N16" t="n">
         <v>0.5717</v>
@@ -4948,6 +5114,22 @@
         </is>
       </c>
       <c r="CN16" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CP16" t="n">
+        <v>1330</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>52</v>
+      </c>
+      <c r="CR16" t="inlineStr">
+        <is>
+          <t>Islamic loans</t>
+        </is>
+      </c>
+      <c r="CS16" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -5009,7 +5191,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>7573</v>
+        <v>8786</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -5017,7 +5199,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.0674</v>
+        <v>0.0781</v>
       </c>
       <c r="N17" t="n">
         <v>0.5416</v>
@@ -5183,6 +5365,22 @@
         </is>
       </c>
       <c r="CN17" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CP17" t="n">
+        <v>1213</v>
+      </c>
+      <c r="CQ17" t="n">
+        <v>78</v>
+      </c>
+      <c r="CR17" t="inlineStr">
+        <is>
+          <t>Islamic loan</t>
+        </is>
+      </c>
+      <c r="CS17" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -5243,10 +5441,16 @@
       <c r="J18" t="b">
         <v>0</v>
       </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>zero</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>-82.8592</v>
@@ -5504,7 +5708,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1246</v>
+        <v>3251</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -5512,7 +5716,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.0111</v>
+        <v>0.0289</v>
       </c>
       <c r="N19" t="n">
         <v>0.5104</v>
@@ -5678,6 +5882,22 @@
         </is>
       </c>
       <c r="CN19" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CP19" t="n">
+        <v>2005</v>
+      </c>
+      <c r="CQ19" t="n">
+        <v>199</v>
+      </c>
+      <c r="CR19" t="inlineStr">
+        <is>
+          <t>Islamic loans</t>
+        </is>
+      </c>
+      <c r="CS19" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -6454,7 +6674,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>1564251</v>
+        <v>7056531</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -6462,7 +6682,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.4505</v>
+        <v>2.0324</v>
       </c>
       <c r="N23" t="n">
         <v>0.7991</v>
@@ -6625,6 +6845,22 @@
         </is>
       </c>
       <c r="CI23" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CP23" t="n">
+        <v>5492280</v>
+      </c>
+      <c r="CQ23" t="n">
+        <v>69</v>
+      </c>
+      <c r="CR23" t="inlineStr">
+        <is>
+          <t>Term loan</t>
+        </is>
+      </c>
+      <c r="CS23" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -7526,9 +7762,12 @@
       <c r="J29" t="b">
         <v>0</v>
       </c>
+      <c r="K29" t="n">
+        <v>3000</v>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>not_found</t>
+          <t>extracted</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -7629,6 +7868,22 @@
       <c r="BK29" t="inlineStr">
         <is>
           <t>assumed 100% parent NP (no NCI attribution row found)</t>
+        </is>
+      </c>
+      <c r="CP29" t="n">
+        <v>3000</v>
+      </c>
+      <c r="CQ29" t="n">
+        <v>23</v>
+      </c>
+      <c r="CR29" t="inlineStr">
+        <is>
+          <t>SIDF loan</t>
+        </is>
+      </c>
+      <c r="CS29" t="inlineStr">
+        <is>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -7671,9 +7926,12 @@
       <c r="J30" t="b">
         <v>0</v>
       </c>
+      <c r="K30" t="n">
+        <v>3000</v>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>not_found</t>
+          <t>extracted</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -7746,6 +8004,22 @@
       <c r="BF30" t="inlineStr">
         <is>
           <t>label found but no number extracted</t>
+        </is>
+      </c>
+      <c r="CP30" t="n">
+        <v>3000</v>
+      </c>
+      <c r="CQ30" t="n">
+        <v>23</v>
+      </c>
+      <c r="CR30" t="inlineStr">
+        <is>
+          <t>SIDF loan</t>
+        </is>
+      </c>
+      <c r="CS30" t="inlineStr">
+        <is>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -7788,9 +8062,12 @@
       <c r="J31" t="b">
         <v>0</v>
       </c>
+      <c r="K31" t="n">
+        <v>3000</v>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>not_found</t>
+          <t>extracted</t>
         </is>
       </c>
       <c r="N31" t="n">
@@ -7847,6 +8124,22 @@
       <c r="BF31" t="inlineStr">
         <is>
           <t>label found but no number extracted</t>
+        </is>
+      </c>
+      <c r="CP31" t="n">
+        <v>3000</v>
+      </c>
+      <c r="CQ31" t="n">
+        <v>23</v>
+      </c>
+      <c r="CR31" t="inlineStr">
+        <is>
+          <t>SIDF loan</t>
+        </is>
+      </c>
+      <c r="CS31" t="inlineStr">
+        <is>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -8081,10 +8374,16 @@
       <c r="J35" t="b">
         <v>0</v>
       </c>
+      <c r="K35" t="n">
+        <v>1777397832344</v>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>235916.6999</v>
       </c>
       <c r="N35" t="n">
         <v>0.4865</v>
@@ -8255,6 +8554,38 @@
         </is>
       </c>
       <c r="BY35" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="CK35" t="n">
+        <v>888698916172</v>
+      </c>
+      <c r="CL35" t="n">
+        <v>45</v>
+      </c>
+      <c r="CM35" t="inlineStr">
+        <is>
+          <t>Bank borrowings</t>
+        </is>
+      </c>
+      <c r="CN35" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="CZ35" t="n">
+        <v>888698916172</v>
+      </c>
+      <c r="DA35" t="n">
+        <v>45</v>
+      </c>
+      <c r="DB35" t="inlineStr">
+        <is>
+          <t>Lease liabilities</t>
+        </is>
+      </c>
+      <c r="DC35" t="inlineStr">
         <is>
           <t>low</t>
         </is>
@@ -8315,10 +8646,16 @@
       <c r="J36" t="b">
         <v>0</v>
       </c>
+      <c r="K36" t="n">
+        <v>1965545777396</v>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>247228.2003</v>
       </c>
       <c r="N36" t="n">
         <v>0.4823</v>
@@ -8514,6 +8851,38 @@
       <c r="CJ36" t="inlineStr">
         <is>
           <t>label found but no number extracted</t>
+        </is>
+      </c>
+      <c r="CK36" t="n">
+        <v>982772888698</v>
+      </c>
+      <c r="CL36" t="n">
+        <v>48</v>
+      </c>
+      <c r="CM36" t="inlineStr">
+        <is>
+          <t>Bank borrowings</t>
+        </is>
+      </c>
+      <c r="CN36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="CZ36" t="n">
+        <v>982772888698</v>
+      </c>
+      <c r="DA36" t="n">
+        <v>48</v>
+      </c>
+      <c r="DB36" t="inlineStr">
+        <is>
+          <t>Lease liabilities</t>
+        </is>
+      </c>
+      <c r="DC36" t="inlineStr">
+        <is>
+          <t>low</t>
         </is>
       </c>
       <c r="EI36" t="n">
@@ -10016,10 +10385,16 @@
       <c r="J43" t="b">
         <v>0</v>
       </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>zero</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>0.863</v>
@@ -11897,10 +12272,16 @@
       <c r="J50" t="b">
         <v>0</v>
       </c>
+      <c r="K50" t="n">
+        <v>7312034</v>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>35.1256</v>
       </c>
       <c r="N50" t="n">
         <v>0.8443000000000001</v>
@@ -12081,6 +12462,22 @@
         </is>
       </c>
       <c r="BT50" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="DE50" t="n">
+        <v>7312034</v>
+      </c>
+      <c r="DF50" t="n">
+        <v>73</v>
+      </c>
+      <c r="DG50" t="inlineStr">
+        <is>
+          <t>Due to SAMA, banks and other financial institutions</t>
+        </is>
+      </c>
+      <c r="DH50" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -12141,10 +12538,16 @@
       <c r="J51" t="b">
         <v>0</v>
       </c>
+      <c r="K51" t="n">
+        <v>15239791</v>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>0.5927</v>
       </c>
       <c r="N51" t="n">
         <v>0.823</v>
@@ -12320,6 +12723,22 @@
         </is>
       </c>
       <c r="BT51" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="DE51" t="n">
+        <v>15239791</v>
+      </c>
+      <c r="DF51" t="n">
+        <v>61</v>
+      </c>
+      <c r="DG51" t="inlineStr">
+        <is>
+          <t>Due to SAMA, banks and other financial institutions</t>
+        </is>
+      </c>
+      <c r="DH51" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -12396,10 +12815,16 @@
       <c r="J52" t="b">
         <v>0</v>
       </c>
+      <c r="K52" t="n">
+        <v>16483039</v>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>0.6133</v>
       </c>
       <c r="N52" t="n">
         <v>0.841</v>
@@ -12575,6 +13000,22 @@
         </is>
       </c>
       <c r="BT52" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="DE52" t="n">
+        <v>16483039</v>
+      </c>
+      <c r="DF52" t="n">
+        <v>120</v>
+      </c>
+      <c r="DG52" t="inlineStr">
+        <is>
+          <t>Due to SAMA, banks and other financial institutions</t>
+        </is>
+      </c>
+      <c r="DH52" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -12651,10 +13092,16 @@
       <c r="J53" t="b">
         <v>0</v>
       </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>zero</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
       </c>
       <c r="N53" t="n">
         <v>-7094.1852</v>
@@ -14932,7 +15379,7 @@
         <v>0</v>
       </c>
       <c r="J62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" t="n">
         <v>5561</v>
@@ -15091,6 +15538,9 @@
           <t>assumed 100% parent NP (no NCI attribution row found)</t>
         </is>
       </c>
+      <c r="BQ62" t="n">
+        <v>0.007</v>
+      </c>
       <c r="BR62" t="n">
         <v>79</v>
       </c>
@@ -15101,12 +15551,12 @@
       </c>
       <c r="BT62" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="BU62" t="inlineStr">
         <is>
-          <t>fils/baisa: value 9755 too large; no valid fils found in 20-line context</t>
+          <t>fils/baisa→BHD: recovered (orig=9755, fils=7.000)</t>
         </is>
       </c>
       <c r="CF62" t="n">
@@ -15195,7 +15645,7 @@
         <v>0</v>
       </c>
       <c r="J63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K63" t="n">
         <v>4864</v>
@@ -15354,6 +15804,9 @@
           <t>assumed 100% parent NP (no NCI attribution row found)</t>
         </is>
       </c>
+      <c r="BQ63" t="n">
+        <v>0.319</v>
+      </c>
       <c r="BR63" t="n">
         <v>105</v>
       </c>
@@ -15364,12 +15817,12 @@
       </c>
       <c r="BT63" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="BU63" t="inlineStr">
         <is>
-          <t>fils/baisa: value 451870 too large; no valid fils found in 20-line context</t>
+          <t>fils/baisa→BHD: recovered (orig=451870, fils=319.000)</t>
         </is>
       </c>
       <c r="CF63" t="n">
@@ -15458,7 +15911,7 @@
         <v>0</v>
       </c>
       <c r="J64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K64" t="n">
         <v>4752</v>
@@ -15617,6 +16070,9 @@
           <t>assumed 100% parent NP (no NCI attribution row found)</t>
         </is>
       </c>
+      <c r="BQ64" t="n">
+        <v>0.294</v>
+      </c>
       <c r="BR64" t="n">
         <v>54</v>
       </c>
@@ -15627,12 +16083,12 @@
       </c>
       <c r="BT64" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="BU64" t="inlineStr">
         <is>
-          <t>fils/baisa: value 416167 too large; no valid fils found in 20-line context</t>
+          <t>fils/baisa→BHD: recovered (orig=416167, fils=294.000)</t>
         </is>
       </c>
       <c r="CF64" t="n">
@@ -15739,7 +16195,7 @@
         <v>0</v>
       </c>
       <c r="J65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K65" t="n">
         <v>7607</v>
@@ -15876,6 +16332,9 @@
           <t>assumed 100% parent NP (no NCI attribution row found)</t>
         </is>
       </c>
+      <c r="BQ65" t="n">
+        <v>0.083</v>
+      </c>
       <c r="BR65" t="n">
         <v>63</v>
       </c>
@@ -15886,12 +16345,12 @@
       </c>
       <c r="BT65" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="BU65" t="inlineStr">
         <is>
-          <t>fils/baisa: value 118025 too large; no valid fils found in 20-line context</t>
+          <t>fils/baisa→BHD: recovered (orig=118025, fils=83.000)</t>
         </is>
       </c>
       <c r="CF65" t="n">
@@ -15996,7 +16455,7 @@
         <v>0</v>
       </c>
       <c r="J66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66" t="n">
         <v>6796</v>
@@ -16133,6 +16592,9 @@
           <t>assumed 100% parent NP (no NCI attribution row found)</t>
         </is>
       </c>
+      <c r="BQ66" t="n">
+        <v>0.13</v>
+      </c>
       <c r="BR66" t="n">
         <v>63</v>
       </c>
@@ -16143,12 +16605,12 @@
       </c>
       <c r="BT66" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="BU66" t="inlineStr">
         <is>
-          <t>fils/baisa: value 184542 too large; no valid fils found in 20-line context</t>
+          <t>fils/baisa→BHD: recovered (orig=184542, fils=130.000)</t>
         </is>
       </c>
       <c r="CF66" t="n">
@@ -16237,7 +16699,7 @@
         <v>0</v>
       </c>
       <c r="J67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K67" t="n">
         <v>11171</v>
@@ -16365,6 +16827,9 @@
           <t>assumed 100% parent NP (no NCI attribution row found)</t>
         </is>
       </c>
+      <c r="BQ67" t="n">
+        <v>0.154</v>
+      </c>
       <c r="BR67" t="n">
         <v>65</v>
       </c>
@@ -16375,12 +16840,12 @@
       </c>
       <c r="BT67" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="BU67" t="inlineStr">
         <is>
-          <t>fils/baisa: value 218687 too large; no valid fils found in 20-line context</t>
+          <t>fils/baisa→BHD: recovered (orig=218687, fils=154.000)</t>
         </is>
       </c>
       <c r="CF67" t="n">
@@ -16469,7 +16934,7 @@
         <v>0</v>
       </c>
       <c r="J68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K68" t="n">
         <v>43852</v>
@@ -16618,6 +17083,9 @@
           <t>high</t>
         </is>
       </c>
+      <c r="BQ68" t="n">
+        <v>0.0342</v>
+      </c>
       <c r="BR68" t="n">
         <v>94</v>
       </c>
@@ -16628,12 +17096,12 @@
       </c>
       <c r="BT68" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="BU68" t="inlineStr">
         <is>
-          <t>fils/baisa: value 60547 too large; no valid fils found in 20-line context</t>
+          <t>fils/baisa→BHD: recovered (orig=60547, fils=34.200)</t>
         </is>
       </c>
       <c r="BV68" t="n">
@@ -16738,7 +17206,7 @@
         <v>0</v>
       </c>
       <c r="J69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K69" t="n">
         <v>46733</v>
@@ -16775,6 +17243,11 @@
       <c r="U69" t="n">
         <v>40</v>
       </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>EPS_MISMATCH: reported=0.0398  computed_ind=108.0464  computed_fin=0.1080  (NPA/shares)</t>
+        </is>
+      </c>
       <c r="X69" t="n">
         <v>1030585</v>
       </c>
@@ -16887,6 +17360,9 @@
           <t>high</t>
         </is>
       </c>
+      <c r="BQ69" t="n">
+        <v>0.0398</v>
+      </c>
       <c r="BR69" t="n">
         <v>38</v>
       </c>
@@ -16897,12 +17373,12 @@
       </c>
       <c r="BT69" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="BU69" t="inlineStr">
         <is>
-          <t>fils/baisa: value 80347 too large; no valid fils found in 20-line context</t>
+          <t>fils/baisa→BHD: recovered (orig=80347, fils=39.800)</t>
         </is>
       </c>
       <c r="BV69" t="n">
@@ -17041,7 +17517,7 @@
         <v>0</v>
       </c>
       <c r="J70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K70" t="n">
         <v>49021</v>
@@ -17078,6 +17554,11 @@
       <c r="U70" t="n">
         <v>0</v>
       </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>EPS_MISMATCH: reported=0.0425  computed_ind=115.3155  computed_fin=0.1153  (NPA/shares)</t>
+        </is>
+      </c>
       <c r="X70" t="n">
         <v>1101161</v>
       </c>
@@ -17190,6 +17671,9 @@
           <t>high</t>
         </is>
       </c>
+      <c r="BQ70" t="n">
+        <v>0.0425</v>
+      </c>
       <c r="BR70" t="n">
         <v>41</v>
       </c>
@@ -17200,12 +17684,12 @@
       </c>
       <c r="BT70" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="BU70" t="inlineStr">
         <is>
-          <t>fils/baisa: value 68253 too large; no valid fils found in 20-line context</t>
+          <t>fils/baisa→BHD: recovered (orig=68253, fils=42.500)</t>
         </is>
       </c>
       <c r="BV70" t="n">
@@ -17344,7 +17828,7 @@
         <v>0</v>
       </c>
       <c r="J71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K71" t="n">
         <v>45776</v>
@@ -17381,6 +17865,11 @@
       <c r="U71" t="n">
         <v>20</v>
       </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>EPS_MISMATCH: reported=0.0436  computed_ind=118.1441  computed_fin=0.1181  (NPA/shares)</t>
+        </is>
+      </c>
       <c r="X71" t="n">
         <v>1165365</v>
       </c>
@@ -17493,6 +17982,9 @@
           <t>high</t>
         </is>
       </c>
+      <c r="BQ71" t="n">
+        <v>0.0436</v>
+      </c>
       <c r="BR71" t="n">
         <v>86</v>
       </c>
@@ -17503,12 +17995,12 @@
       </c>
       <c r="BT71" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="BU71" t="inlineStr">
         <is>
-          <t>fils/baisa: value 101610 too large; no valid fils found in 20-line context</t>
+          <t>fils/baisa→BHD: recovered (orig=101610, fils=43.600)</t>
         </is>
       </c>
       <c r="BV71" t="n">
@@ -17613,7 +18105,7 @@
         <v>0</v>
       </c>
       <c r="J72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72" t="n">
         <v>322589</v>
@@ -17650,6 +18142,11 @@
       <c r="U72" t="n">
         <v>43</v>
       </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>EPS_MISMATCH: reported=0.0440  computed_ind=119.3018  computed_fin=0.1193  (NPA/shares)</t>
+        </is>
+      </c>
       <c r="X72" t="n">
         <v>1256009</v>
       </c>
@@ -17762,6 +18259,9 @@
           <t>high</t>
         </is>
       </c>
+      <c r="BQ72" t="n">
+        <v>0.044</v>
+      </c>
       <c r="BR72" t="n">
         <v>48</v>
       </c>
@@ -17772,12 +18272,12 @@
       </c>
       <c r="BT72" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="BU72" t="inlineStr">
         <is>
-          <t>fils/baisa: value 112483 too large; no valid fils found in 20-line context</t>
+          <t>fils/baisa→BHD: recovered (orig=112483, fils=44.000)</t>
         </is>
       </c>
       <c r="BV72" t="n">
@@ -17916,7 +18416,7 @@
         <v>0</v>
       </c>
       <c r="J73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" t="n">
         <v>355637</v>
@@ -17953,6 +18453,11 @@
       <c r="U73" t="n">
         <v>43</v>
       </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>EPS_MISMATCH: reported=0.0432  computed_ind=116.9602  computed_fin=0.1170  (NPA/shares)</t>
+        </is>
+      </c>
       <c r="X73" t="n">
         <v>1305493</v>
       </c>
@@ -18065,6 +18570,9 @@
           <t>high</t>
         </is>
       </c>
+      <c r="BQ73" t="n">
+        <v>0.0432</v>
+      </c>
       <c r="BR73" t="n">
         <v>46</v>
       </c>
@@ -18075,12 +18583,12 @@
       </c>
       <c r="BT73" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="BU73" t="inlineStr">
         <is>
-          <t>fils/baisa: value 79037 too large; no valid fils found in 20-line context</t>
+          <t>fils/baisa→BHD: recovered (orig=79037, fils=43.200)</t>
         </is>
       </c>
       <c r="BV73" t="n">
@@ -18492,7 +19000,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>79726159</v>
+        <v>1299731928</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -18635,17 +19143,33 @@
         </is>
       </c>
       <c r="CK75" t="n">
-        <v>51321755</v>
+        <v>78000000</v>
       </c>
       <c r="CL75" t="n">
         <v>115</v>
       </c>
       <c r="CM75" t="inlineStr">
         <is>
-          <t>Short term borrowings</t>
+          <t>Current portion of Islamic financing</t>
         </is>
       </c>
       <c r="CN75" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CP75" t="n">
+        <v>1193327524</v>
+      </c>
+      <c r="CQ75" t="n">
+        <v>115</v>
+      </c>
+      <c r="CR75" t="inlineStr">
+        <is>
+          <t>Islamic financing</t>
+        </is>
+      </c>
+      <c r="CS75" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -18734,7 +19258,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>108298200</v>
+        <v>1729126484</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -18861,17 +19385,33 @@
         </is>
       </c>
       <c r="CK76" t="n">
-        <v>99492839</v>
+        <v>86125000</v>
       </c>
       <c r="CL76" t="n">
         <v>131</v>
       </c>
       <c r="CM76" t="inlineStr">
         <is>
-          <t>Bank overdrafts</t>
+          <t>Current portion of Islamic financing</t>
         </is>
       </c>
       <c r="CN76" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CP76" t="n">
+        <v>1634196123</v>
+      </c>
+      <c r="CQ76" t="n">
+        <v>131</v>
+      </c>
+      <c r="CR76" t="inlineStr">
+        <is>
+          <t>Islamic financing</t>
+        </is>
+      </c>
+      <c r="CS76" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -19650,10 +20190,16 @@
       <c r="J80" t="b">
         <v>0</v>
       </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>zero</t>
+        </is>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
       </c>
       <c r="N80" t="n">
         <v>-990.3528</v>
@@ -19915,10 +20461,16 @@
       <c r="J81" t="b">
         <v>0</v>
       </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>zero</t>
+        </is>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
       </c>
       <c r="N81" t="n">
         <v>0.9917</v>
@@ -20139,10 +20691,16 @@
       <c r="J82" t="b">
         <v>0</v>
       </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>zero</t>
+        </is>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
       </c>
       <c r="N82" t="n">
         <v>0.989</v>
@@ -20345,10 +20903,16 @@
       <c r="J83" t="b">
         <v>0</v>
       </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>zero</t>
+        </is>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
       </c>
       <c r="N83" t="n">
         <v>0.8934</v>
@@ -20667,10 +21231,16 @@
       <c r="J85" t="b">
         <v>0</v>
       </c>
+      <c r="K85" t="n">
+        <v>6088814</v>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="M85" t="n">
+        <v>0.3219</v>
       </c>
       <c r="N85" t="n">
         <v>0.8764999999999999</v>
@@ -20862,6 +21432,38 @@
         </is>
       </c>
       <c r="BY85" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="DJ85" t="n">
+        <v>3044407</v>
+      </c>
+      <c r="DK85" t="n">
+        <v>172</v>
+      </c>
+      <c r="DL85" t="inlineStr">
+        <is>
+          <t>Tier 2 Sukuk</t>
+        </is>
+      </c>
+      <c r="DM85" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="DO85" t="n">
+        <v>3044407</v>
+      </c>
+      <c r="DP85" t="n">
+        <v>172</v>
+      </c>
+      <c r="DQ85" t="inlineStr">
+        <is>
+          <t>Tier 2 Sukuk</t>
+        </is>
+      </c>
+      <c r="DR85" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -21097,6 +21699,22 @@
           <t>assumed 100% parent NP (no NCI attribution row found)</t>
         </is>
       </c>
+      <c r="CF86" t="n">
+        <v>483556</v>
+      </c>
+      <c r="CG86" t="n">
+        <v>383</v>
+      </c>
+      <c r="CH86" t="inlineStr">
+        <is>
+          <t>Total financing</t>
+        </is>
+      </c>
+      <c r="CI86" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
       <c r="DE86" t="n">
         <v>50000</v>
       </c>
@@ -21277,6 +21895,22 @@
           <t>assumed 100% parent NP (no NCI attribution row found)</t>
         </is>
       </c>
+      <c r="CF87" t="n">
+        <v>501255</v>
+      </c>
+      <c r="CG87" t="n">
+        <v>367</v>
+      </c>
+      <c r="CH87" t="inlineStr">
+        <is>
+          <t>Total financing</t>
+        </is>
+      </c>
+      <c r="CI87" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
       <c r="DE87" t="n">
         <v>50000</v>
       </c>
@@ -21349,10 +21983,16 @@
       <c r="J88" t="b">
         <v>0</v>
       </c>
+      <c r="K88" t="n">
+        <v>555481</v>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="M88" t="n">
+        <v>86.9706</v>
       </c>
       <c r="N88" t="n">
         <v>0.8991</v>
@@ -21500,6 +22140,22 @@
       <c r="BK88" t="inlineStr">
         <is>
           <t>assumed 100% parent NP (no NCI attribution row found)</t>
+        </is>
+      </c>
+      <c r="CF88" t="n">
+        <v>555481</v>
+      </c>
+      <c r="CG88" t="n">
+        <v>194</v>
+      </c>
+      <c r="CH88" t="inlineStr">
+        <is>
+          <t>Total financing</t>
+        </is>
+      </c>
+      <c r="CI88" t="inlineStr">
+        <is>
+          <t>high</t>
         </is>
       </c>
       <c r="EI88" t="n">
@@ -21558,10 +22214,16 @@
       <c r="J89" t="b">
         <v>0</v>
       </c>
+      <c r="K89" t="n">
+        <v>672091</v>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="M89" t="n">
+        <v>50.0179</v>
       </c>
       <c r="N89" t="n">
         <v>0.9368</v>
@@ -21709,6 +22371,22 @@
       <c r="BK89" t="inlineStr">
         <is>
           <t>assumed 100% parent NP (no NCI attribution row found)</t>
+        </is>
+      </c>
+      <c r="CF89" t="n">
+        <v>672091</v>
+      </c>
+      <c r="CG89" t="n">
+        <v>356</v>
+      </c>
+      <c r="CH89" t="inlineStr">
+        <is>
+          <t>Total financing</t>
+        </is>
+      </c>
+      <c r="CI89" t="inlineStr">
+        <is>
+          <t>high</t>
         </is>
       </c>
       <c r="EI89" t="n">
@@ -26710,7 +27388,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>1118784</v>
+        <v>2951234</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -26718,7 +27396,7 @@
         </is>
       </c>
       <c r="M110" t="n">
-        <v>0.0589</v>
+        <v>0.1553</v>
       </c>
       <c r="N110" t="n">
         <v>-1.5945</v>
@@ -26896,6 +27574,22 @@
         </is>
       </c>
       <c r="CS110" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CU110" t="n">
+        <v>1832450</v>
+      </c>
+      <c r="CV110" t="n">
+        <v>60</v>
+      </c>
+      <c r="CW110" t="inlineStr">
+        <is>
+          <t>Islamic Sukuk</t>
+        </is>
+      </c>
+      <c r="CX110" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -26941,7 +27635,7 @@
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>2447696</v>
+        <v>5251746</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -26949,7 +27643,7 @@
         </is>
       </c>
       <c r="M111" t="n">
-        <v>0.1286</v>
+        <v>0.276</v>
       </c>
       <c r="N111" t="n">
         <v>-0.9451000000000001</v>
@@ -27143,6 +27837,22 @@
         </is>
       </c>
       <c r="CS111" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CU111" t="n">
+        <v>2804050</v>
+      </c>
+      <c r="CV111" t="n">
+        <v>67</v>
+      </c>
+      <c r="CW111" t="inlineStr">
+        <is>
+          <t>Islamic Sukuk</t>
+        </is>
+      </c>
+      <c r="CX111" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -27187,10 +27897,16 @@
       <c r="J112" t="b">
         <v>0</v>
       </c>
+      <c r="K112" t="n">
+        <v>1967988</v>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="M112" t="n">
+        <v>39.217</v>
       </c>
       <c r="N112" t="n">
         <v>0.9929</v>
@@ -27357,6 +28073,22 @@
         </is>
       </c>
       <c r="BY112" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CU112" t="n">
+        <v>1967988</v>
+      </c>
+      <c r="CV112" t="n">
+        <v>82</v>
+      </c>
+      <c r="CW112" t="inlineStr">
+        <is>
+          <t>Islamic Sukuk</t>
+        </is>
+      </c>
+      <c r="CX112" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -27401,10 +28133,16 @@
       <c r="J113" t="b">
         <v>0</v>
       </c>
+      <c r="K113" t="n">
+        <v>3715302</v>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="M113" t="n">
+        <v>73.9408</v>
       </c>
       <c r="N113" t="n">
         <v>0.9936</v>
@@ -27571,6 +28309,22 @@
         </is>
       </c>
       <c r="BY113" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CU113" t="n">
+        <v>3715302</v>
+      </c>
+      <c r="CV113" t="n">
+        <v>88</v>
+      </c>
+      <c r="CW113" t="inlineStr">
+        <is>
+          <t>Islamic Sukuk</t>
+        </is>
+      </c>
+      <c r="CX113" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -27616,7 +28370,7 @@
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>5236</v>
+        <v>2971773</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -27624,7 +28378,7 @@
         </is>
       </c>
       <c r="M114" t="n">
-        <v>0.8575</v>
+        <v>486.6972</v>
       </c>
       <c r="N114" t="n">
         <v>1.1957</v>
@@ -27797,6 +28551,38 @@
         </is>
       </c>
       <c r="CI114" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CU114" t="n">
+        <v>2663200</v>
+      </c>
+      <c r="CV114" t="n">
+        <v>113</v>
+      </c>
+      <c r="CW114" t="inlineStr">
+        <is>
+          <t>Islamic Sukuk</t>
+        </is>
+      </c>
+      <c r="CX114" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CZ114" t="n">
+        <v>308573</v>
+      </c>
+      <c r="DA114" t="n">
+        <v>124</v>
+      </c>
+      <c r="DB114" t="inlineStr">
+        <is>
+          <t>Lease liabilities</t>
+        </is>
+      </c>
+      <c r="DC114" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -27842,7 +28628,7 @@
         <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>5236</v>
+        <v>4302828</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -27850,7 +28636,7 @@
         </is>
       </c>
       <c r="M115" t="n">
-        <v>0.8575</v>
+        <v>704.6885</v>
       </c>
       <c r="N115" t="n">
         <v>1.3357</v>
@@ -28023,6 +28809,38 @@
         </is>
       </c>
       <c r="CI115" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CU115" t="n">
+        <v>3994255</v>
+      </c>
+      <c r="CV115" t="n">
+        <v>149</v>
+      </c>
+      <c r="CW115" t="inlineStr">
+        <is>
+          <t>Islamic Sukuk</t>
+        </is>
+      </c>
+      <c r="CX115" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CZ115" t="n">
+        <v>308573</v>
+      </c>
+      <c r="DA115" t="n">
+        <v>161</v>
+      </c>
+      <c r="DB115" t="inlineStr">
+        <is>
+          <t>Lease liabilities</t>
+        </is>
+      </c>
+      <c r="DC115" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -28068,7 +28886,7 @@
         <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>6090948</v>
+        <v>7113903</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -28076,7 +28894,7 @@
         </is>
       </c>
       <c r="M116" t="n">
-        <v>238.842</v>
+        <v>278.9547</v>
       </c>
       <c r="N116" t="n">
         <v>-13.9397</v>
@@ -28230,6 +29048,22 @@
         </is>
       </c>
       <c r="CI116" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CK116" t="n">
+        <v>1022955</v>
+      </c>
+      <c r="CL116" t="n">
+        <v>51</v>
+      </c>
+      <c r="CM116" t="inlineStr">
+        <is>
+          <t>Short term loans</t>
+        </is>
+      </c>
+      <c r="CN116" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -31990,10 +32824,16 @@
       <c r="J131" t="b">
         <v>0</v>
       </c>
+      <c r="K131" t="n">
+        <v>9171882</v>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="M131" t="n">
+        <v>118.0058</v>
       </c>
       <c r="N131" t="n">
         <v>0.3771</v>
@@ -32166,6 +33006,40 @@
         </is>
       </c>
       <c r="CJ131" t="inlineStr">
+        <is>
+          <t>label found but no number extracted</t>
+        </is>
+      </c>
+      <c r="CU131" t="n">
+        <v>9171882</v>
+      </c>
+      <c r="CV131" t="n">
+        <v>87</v>
+      </c>
+      <c r="CW131" t="inlineStr">
+        <is>
+          <t>Sukuk</t>
+        </is>
+      </c>
+      <c r="CX131" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="DA131" t="n">
+        <v>95</v>
+      </c>
+      <c r="DB131" t="inlineStr">
+        <is>
+          <t>Lease liabilities</t>
+        </is>
+      </c>
+      <c r="DC131" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="DD131" t="inlineStr">
         <is>
           <t>label found but no number extracted</t>
         </is>
@@ -35110,7 +35984,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>4669</v>
+        <v>16152</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -35252,6 +36126,22 @@
       <c r="CJ146" t="inlineStr">
         <is>
           <t>label found but no number extracted</t>
+        </is>
+      </c>
+      <c r="CP146" t="n">
+        <v>11483</v>
+      </c>
+      <c r="CQ146" t="n">
+        <v>93</v>
+      </c>
+      <c r="CR146" t="inlineStr">
+        <is>
+          <t>Long-term loans</t>
+        </is>
+      </c>
+      <c r="CS146" t="inlineStr">
+        <is>
+          <t>high</t>
         </is>
       </c>
       <c r="CZ146" t="n">
@@ -36414,10 +37304,16 @@
       <c r="J152" t="b">
         <v>0</v>
       </c>
+      <c r="K152" t="n">
+        <v>58103281</v>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="M152" t="n">
+        <v>24516.1523</v>
       </c>
       <c r="N152" t="n">
         <v>0.8814</v>
@@ -36555,6 +37451,38 @@
         </is>
       </c>
       <c r="BT152" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="DE152" t="n">
+        <v>57632476</v>
+      </c>
+      <c r="DF152" t="n">
+        <v>152</v>
+      </c>
+      <c r="DG152" t="inlineStr">
+        <is>
+          <t>Due to banks and financial institutions</t>
+        </is>
+      </c>
+      <c r="DH152" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="DO152" t="n">
+        <v>470805</v>
+      </c>
+      <c r="DP152" t="n">
+        <v>152</v>
+      </c>
+      <c r="DQ152" t="inlineStr">
+        <is>
+          <t>Subordinated notes</t>
+        </is>
+      </c>
+      <c r="DR152" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -37915,12 +38843,18 @@
         <v>0</v>
       </c>
       <c r="J158" t="b">
+        <v>1</v>
+      </c>
+      <c r="K158" t="n">
         <v>0</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>zero</t>
+        </is>
+      </c>
+      <c r="M158" t="n">
+        <v>0</v>
       </c>
       <c r="N158" t="n">
         <v>0.1529</v>
@@ -37943,6 +38877,11 @@
       <c r="T158" t="n">
         <v>14.7726</v>
       </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>EPS_MISMATCH: reported=-0.0360  computed_ind=772106.7267  computed_fin=772.1067  (NPA/shares)</t>
+        </is>
+      </c>
       <c r="X158" t="n">
         <v>118780233</v>
       </c>
@@ -38065,6 +39004,9 @@
           <t>assumed 100% parent NP (no NCI attribution row found)</t>
         </is>
       </c>
+      <c r="BQ158" t="n">
+        <v>-0.036</v>
+      </c>
       <c r="BR158" t="n">
         <v>34</v>
       </c>
@@ -38075,12 +39017,12 @@
       </c>
       <c r="BT158" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="BU158" t="inlineStr">
         <is>
-          <t>fils/baisa: value -8127985 too large; no valid fils found in 20-line context</t>
+          <t>fils/baisa→BHD: recovered (orig=-8127985, fils=-36.000)</t>
         </is>
       </c>
       <c r="BV158" t="n">
@@ -38153,12 +39095,18 @@
         <v>0</v>
       </c>
       <c r="J159" t="b">
+        <v>1</v>
+      </c>
+      <c r="K159" t="n">
         <v>0</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>zero</t>
+        </is>
+      </c>
+      <c r="M159" t="n">
+        <v>0</v>
       </c>
       <c r="N159" t="n">
         <v>0.1024</v>
@@ -38181,6 +39129,11 @@
       <c r="T159" t="n">
         <v>14.8195</v>
       </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>EPS_MISMATCH: reported=0.0150  computed_ind=150.2839  computed_fin=0.1503  (NPA/shares)</t>
+        </is>
+      </c>
       <c r="X159" t="n">
         <v>113446493</v>
       </c>
@@ -38303,6 +39256,9 @@
           <t>assumed 100% parent NP (no NCI attribution row found)</t>
         </is>
       </c>
+      <c r="BQ159" t="n">
+        <v>0.015</v>
+      </c>
       <c r="BR159" t="n">
         <v>44</v>
       </c>
@@ -38313,12 +39269,12 @@
       </c>
       <c r="BT159" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="BU159" t="inlineStr">
         <is>
-          <t>fils/baisa: value 3396338 too large; no valid fils found in 20-line context</t>
+          <t>fils/baisa→BHD: recovered (orig=3396338, fils=15.000)</t>
         </is>
       </c>
       <c r="BV159" t="n">
@@ -38375,12 +39331,18 @@
         <v>0</v>
       </c>
       <c r="J160" t="b">
+        <v>1</v>
+      </c>
+      <c r="K160" t="n">
         <v>0</v>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>zero</t>
+        </is>
+      </c>
+      <c r="M160" t="n">
+        <v>0</v>
       </c>
       <c r="N160" t="n">
         <v>0.0733</v>
@@ -38406,6 +39368,11 @@
       <c r="U160" t="n">
         <v>0</v>
       </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>EPS_MISMATCH: reported=0.0150  computed_ind=295.0959  computed_fin=0.2951  (NPA/shares)</t>
+        </is>
+      </c>
       <c r="X160" t="n">
         <v>111794685</v>
       </c>
@@ -38528,6 +39495,9 @@
           <t>assumed 100% parent NP (no NCI attribution row found)</t>
         </is>
       </c>
+      <c r="BQ160" t="n">
+        <v>0.015</v>
+      </c>
       <c r="BR160" t="n">
         <v>54</v>
       </c>
@@ -38538,12 +39508,12 @@
       </c>
       <c r="BT160" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="BU160" t="inlineStr">
         <is>
-          <t>fils/baisa: value 6327593 too large; no valid fils found in 20-line context</t>
+          <t>fils/baisa→BHD: recovered (orig=6327593, fils=15.000)</t>
         </is>
       </c>
       <c r="BV160" t="n">
@@ -38616,12 +39586,18 @@
         <v>0</v>
       </c>
       <c r="J161" t="b">
+        <v>1</v>
+      </c>
+      <c r="K161" t="n">
         <v>0</v>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>zero</t>
+        </is>
+      </c>
+      <c r="M161" t="n">
+        <v>0</v>
       </c>
       <c r="N161" t="n">
         <v>0.0556</v>
@@ -38647,6 +39623,11 @@
       <c r="U161" t="n">
         <v>0</v>
       </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>EPS_MISMATCH: reported=0.0300  computed_ind=300.2540  computed_fin=0.3003  (NPA/shares)</t>
+        </is>
+      </c>
       <c r="X161" t="n">
         <v>110502354</v>
       </c>
@@ -38769,6 +39750,9 @@
           <t>assumed 100% parent NP (no NCI attribution row found)</t>
         </is>
       </c>
+      <c r="BQ161" t="n">
+        <v>0.03</v>
+      </c>
       <c r="BR161" t="n">
         <v>49</v>
       </c>
@@ -38779,12 +39763,12 @@
       </c>
       <c r="BT161" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="BU161" t="inlineStr">
         <is>
-          <t>fils/baisa: value -653020 too large; no valid fils found in 20-line context</t>
+          <t>fils/baisa→BHD: recovered (orig=-653020, fils=30.000)</t>
         </is>
       </c>
       <c r="BV161" t="n">
@@ -38857,12 +39841,18 @@
         <v>0</v>
       </c>
       <c r="J162" t="b">
+        <v>1</v>
+      </c>
+      <c r="K162" t="n">
         <v>0</v>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>zero</t>
+        </is>
+      </c>
+      <c r="M162" t="n">
+        <v>0</v>
       </c>
       <c r="N162" t="n">
         <v>0.0649</v>
@@ -38888,6 +39878,11 @@
       <c r="U162" t="n">
         <v>0</v>
       </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>EPS_MISMATCH: reported=0.0390  computed_ind=2071.3929  computed_fin=2.0714  (NPA/shares)</t>
+        </is>
+      </c>
       <c r="X162" t="n">
         <v>112861985</v>
       </c>
@@ -39030,6 +40025,9 @@
           <t>assumed 100% parent NP (no NCI attribution row found)</t>
         </is>
       </c>
+      <c r="BQ162" t="n">
+        <v>0.039</v>
+      </c>
       <c r="BR162" t="n">
         <v>140</v>
       </c>
@@ -39040,12 +40038,12 @@
       </c>
       <c r="BT162" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="BU162" t="inlineStr">
         <is>
-          <t>fils/baisa: value 225994863 too large; no valid fils found in 20-line context</t>
+          <t>fils/baisa→BHD: recovered (orig=225994863, fils=39.000)</t>
         </is>
       </c>
       <c r="BV162" t="n">
@@ -39118,12 +40116,18 @@
         <v>0</v>
       </c>
       <c r="J163" t="b">
+        <v>1</v>
+      </c>
+      <c r="K163" t="n">
         <v>0</v>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>zero</t>
+        </is>
+      </c>
+      <c r="M163" t="n">
+        <v>0</v>
       </c>
       <c r="N163" t="n">
         <v>0.0575</v>
@@ -39149,6 +40153,11 @@
       <c r="U163" t="n">
         <v>0</v>
       </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>EPS_MISMATCH: reported=0.0430  computed_ind=432.7912  computed_fin=0.4328  (NPA/shares)</t>
+        </is>
+      </c>
       <c r="X163" t="n">
         <v>116977461</v>
       </c>
@@ -39271,6 +40280,9 @@
           <t>assumed 100% parent NP (no NCI attribution row found)</t>
         </is>
       </c>
+      <c r="BQ163" t="n">
+        <v>0.043</v>
+      </c>
       <c r="BR163" t="n">
         <v>47</v>
       </c>
@@ -39281,12 +40293,12 @@
       </c>
       <c r="BT163" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="BU163" t="inlineStr">
         <is>
-          <t>fils/baisa: value 671389 too large; no valid fils found in 20-line context</t>
+          <t>fils/baisa→BHD: recovered (orig=671389, fils=43.000)</t>
         </is>
       </c>
       <c r="BV163" t="n">
@@ -42537,7 +43549,7 @@
         <v>1</v>
       </c>
       <c r="K182" t="n">
-        <v>81350304</v>
+        <v>89209660</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
@@ -42545,7 +43557,7 @@
         </is>
       </c>
       <c r="M182" t="n">
-        <v>6.7926</v>
+        <v>7.4489</v>
       </c>
       <c r="N182" t="n">
         <v>0.904</v>
@@ -42695,17 +43707,33 @@
         </is>
       </c>
       <c r="CK182" t="n">
-        <v>4418688</v>
+        <v>6139022</v>
       </c>
       <c r="CL182" t="n">
         <v>25</v>
       </c>
       <c r="CM182" t="inlineStr">
         <is>
-          <t>Bank overdrafts</t>
+          <t>Murabaha payables</t>
         </is>
       </c>
       <c r="CN182" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CP182" t="n">
+        <v>6139022</v>
+      </c>
+      <c r="CQ182" t="n">
+        <v>25</v>
+      </c>
+      <c r="CR182" t="inlineStr">
+        <is>
+          <t>Murabaha payables</t>
+        </is>
+      </c>
+      <c r="CS182" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -42783,7 +43811,7 @@
         <v>0</v>
       </c>
       <c r="K183" t="n">
-        <v>137310812</v>
+        <v>126717171</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
@@ -42791,7 +43819,7 @@
         </is>
       </c>
       <c r="M183" t="n">
-        <v>4.5642</v>
+        <v>4.212</v>
       </c>
       <c r="N183" t="n">
         <v>0.8663999999999999</v>
@@ -42955,19 +43983,45 @@
         </is>
       </c>
       <c r="CK183" t="n">
-        <v>21165461</v>
+        <v>5285910</v>
       </c>
       <c r="CL183" t="n">
         <v>24</v>
       </c>
       <c r="CM183" t="inlineStr">
         <is>
-          <t>Bank overdrafts</t>
+          <t>Murabaha payables</t>
         </is>
       </c>
       <c r="CN183" t="inlineStr">
         <is>
           <t>high</t>
+        </is>
+      </c>
+      <c r="CO183" t="inlineStr">
+        <is>
+          <t>coordinate extraction</t>
+        </is>
+      </c>
+      <c r="CP183" t="n">
+        <v>5285910</v>
+      </c>
+      <c r="CQ183" t="n">
+        <v>24</v>
+      </c>
+      <c r="CR183" t="inlineStr">
+        <is>
+          <t>Murabaha payables</t>
+        </is>
+      </c>
+      <c r="CS183" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CT183" t="inlineStr">
+        <is>
+          <t>coordinate extraction</t>
         </is>
       </c>
       <c r="CZ183" t="n">
@@ -43048,7 +44102,7 @@
         <v>1</v>
       </c>
       <c r="K184" t="n">
-        <v>134376013</v>
+        <v>142249972</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
@@ -43056,7 +44110,7 @@
         </is>
       </c>
       <c r="M184" t="n">
-        <v>3.6788</v>
+        <v>3.8944</v>
       </c>
       <c r="N184" t="n">
         <v>0.8658</v>
@@ -43241,14 +44295,14 @@
         </is>
       </c>
       <c r="CK184" t="n">
-        <v>977311</v>
+        <v>4425635</v>
       </c>
       <c r="CL184" t="n">
         <v>22</v>
       </c>
       <c r="CM184" t="inlineStr">
         <is>
-          <t>Bank overdrafts</t>
+          <t>Murabaha payables</t>
         </is>
       </c>
       <c r="CN184" t="inlineStr">
@@ -43257,6 +44311,27 @@
         </is>
       </c>
       <c r="CO184" t="inlineStr">
+        <is>
+          <t>coordinate extraction</t>
+        </is>
+      </c>
+      <c r="CP184" t="n">
+        <v>4425635</v>
+      </c>
+      <c r="CQ184" t="n">
+        <v>22</v>
+      </c>
+      <c r="CR184" t="inlineStr">
+        <is>
+          <t>Murabaha payables</t>
+        </is>
+      </c>
+      <c r="CS184" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CT184" t="inlineStr">
         <is>
           <t>coordinate extraction</t>
         </is>
@@ -43336,7 +44411,7 @@
         <v>0</v>
       </c>
       <c r="J185" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K185" t="n">
         <v>131169352</v>
@@ -43520,6 +44595,9 @@
           <t>assumed 100% parent NP (no NCI attribution row found)</t>
         </is>
       </c>
+      <c r="BQ185" t="n">
+        <v>0.02786</v>
+      </c>
       <c r="BR185" t="n">
         <v>86</v>
       </c>
@@ -43530,12 +44608,12 @@
       </c>
       <c r="BT185" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="BU185" t="inlineStr">
         <is>
-          <t>fils/baisa: value 51465 too large; no valid fils found in 20-line context</t>
+          <t>fils/baisa→KWD: recovered (orig=51465, fils=27.860)</t>
         </is>
       </c>
       <c r="CK185" t="n">
@@ -43637,7 +44715,7 @@
         <v>1</v>
       </c>
       <c r="K186" t="n">
-        <v>123545894</v>
+        <v>234254065</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
@@ -43645,7 +44723,7 @@
         </is>
       </c>
       <c r="M186" t="n">
-        <v>3.4864</v>
+        <v>6.6106</v>
       </c>
       <c r="N186" t="n">
         <v>0.8947000000000001</v>
@@ -43856,6 +44934,27 @@
         </is>
       </c>
       <c r="CO186" t="inlineStr">
+        <is>
+          <t>coordinate extraction</t>
+        </is>
+      </c>
+      <c r="CP186" t="n">
+        <v>110708171</v>
+      </c>
+      <c r="CQ186" t="n">
+        <v>40</v>
+      </c>
+      <c r="CR186" t="inlineStr">
+        <is>
+          <t>Term loan</t>
+        </is>
+      </c>
+      <c r="CS186" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CT186" t="inlineStr">
         <is>
           <t>coordinate extraction</t>
         </is>
@@ -43938,7 +45037,7 @@
         <v>1</v>
       </c>
       <c r="K187" t="n">
-        <v>99399556</v>
+        <v>136291223</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
@@ -43946,7 +45045,7 @@
         </is>
       </c>
       <c r="M187" t="n">
-        <v>2.094</v>
+        <v>2.8712</v>
       </c>
       <c r="N187" t="n">
         <v>0.8574000000000001</v>
@@ -44157,6 +45256,27 @@
         </is>
       </c>
       <c r="CE187" t="inlineStr">
+        <is>
+          <t>coordinate extraction</t>
+        </is>
+      </c>
+      <c r="CP187" t="n">
+        <v>36891667</v>
+      </c>
+      <c r="CQ187" t="n">
+        <v>46</v>
+      </c>
+      <c r="CR187" t="inlineStr">
+        <is>
+          <t>Term loans</t>
+        </is>
+      </c>
+      <c r="CS187" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CT187" t="inlineStr">
         <is>
           <t>coordinate extraction</t>
         </is>
@@ -47283,7 +48403,7 @@
         <v>1</v>
       </c>
       <c r="J200" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K200" t="n">
         <v>0</v>
@@ -47436,6 +48556,9 @@
           <t>assumed 100% parent NP (no NCI attribution row found)</t>
         </is>
       </c>
+      <c r="BQ200" t="n">
+        <v>0.026</v>
+      </c>
       <c r="BR200" t="n">
         <v>96</v>
       </c>
@@ -47446,12 +48569,12 @@
       </c>
       <c r="BT200" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="BU200" t="inlineStr">
         <is>
-          <t>label found but no number extracted</t>
+          <t>fils/baisa→KWD: recovered (orig=None, fils=26.000)</t>
         </is>
       </c>
       <c r="DA200" t="n">
@@ -47510,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="J201" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K201" t="n">
         <v>0</v>
@@ -47669,6 +48792,9 @@
           <t>assumed 100% parent NP (no NCI attribution row found)</t>
         </is>
       </c>
+      <c r="BQ201" t="n">
+        <v>0.09</v>
+      </c>
       <c r="BR201" t="n">
         <v>76</v>
       </c>
@@ -47679,12 +48805,12 @@
       </c>
       <c r="BT201" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="BU201" t="inlineStr">
         <is>
-          <t>fils/baisa: value 44873 too large; no valid fils found in 20-line context</t>
+          <t>fils/baisa→KWD: recovered (orig=44873, fils=90.000)</t>
         </is>
       </c>
       <c r="DA201" t="n">
@@ -47759,7 +48885,7 @@
         <v>0</v>
       </c>
       <c r="J202" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K202" t="n">
         <v>2014</v>
@@ -47880,6 +49006,9 @@
           <t>assumed 100% parent NP (no NCI attribution row found)</t>
         </is>
       </c>
+      <c r="BQ202" t="n">
+        <v>0.031</v>
+      </c>
       <c r="BR202" t="n">
         <v>85</v>
       </c>
@@ -47890,12 +49019,12 @@
       </c>
       <c r="BT202" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="BU202" t="inlineStr">
         <is>
-          <t>fils/baisa: value 33209 too large; no valid fils found in 20-line context</t>
+          <t>fils/baisa→KWD: recovered (orig=33209, fils=31.000)</t>
         </is>
       </c>
       <c r="CK202" t="n">
@@ -47981,7 +49110,7 @@
         <v>0</v>
       </c>
       <c r="J203" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K203" t="n">
         <v>15132</v>
@@ -48102,6 +49231,9 @@
           <t>assumed 100% parent NP (no NCI attribution row found)</t>
         </is>
       </c>
+      <c r="BQ203" t="n">
+        <v>0.033</v>
+      </c>
       <c r="BR203" t="n">
         <v>95</v>
       </c>
@@ -48112,12 +49244,12 @@
       </c>
       <c r="BT203" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="BU203" t="inlineStr">
         <is>
-          <t>fils/baisa: value 32678 too large; no valid fils found in 20-line context</t>
+          <t>fils/baisa→KWD: recovered (orig=32678, fils=33.000)</t>
         </is>
       </c>
       <c r="CK203" t="n">
@@ -48201,7 +49333,7 @@
         <v>0</v>
       </c>
       <c r="J204" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K204" t="n">
         <v>20269</v>
@@ -48323,7 +49455,7 @@
         </is>
       </c>
       <c r="BQ204" t="n">
-        <v>31380</v>
+        <v>0.031</v>
       </c>
       <c r="BR204" t="n">
         <v>88</v>
@@ -48335,7 +49467,12 @@
       </c>
       <c r="BT204" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="BU204" t="inlineStr">
+        <is>
+          <t>fils/baisa→KWD: recovered (orig=31380, fils=31.000)</t>
         </is>
       </c>
       <c r="CZ204" t="n">
@@ -48403,7 +49540,7 @@
         <v>0</v>
       </c>
       <c r="J205" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K205" t="n">
         <v>18470</v>
@@ -48562,6 +49699,9 @@
           <t>assumed 100% parent NP (no NCI attribution row found)</t>
         </is>
       </c>
+      <c r="BQ205" t="n">
+        <v>0.034</v>
+      </c>
       <c r="BR205" t="n">
         <v>91</v>
       </c>
@@ -48572,12 +49712,12 @@
       </c>
       <c r="BT205" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="BU205" t="inlineStr">
         <is>
-          <t>fils/baisa: value 34099 too large; no valid fils found in 20-line context</t>
+          <t>fils/baisa→KWD: recovered (orig=34099, fils=34.000)</t>
         </is>
       </c>
       <c r="CZ205" t="n">
@@ -52123,7 +53263,7 @@
         <v>0</v>
       </c>
       <c r="K222" t="n">
-        <v>738383026</v>
+        <v>190938139</v>
       </c>
       <c r="L222" t="inlineStr">
         <is>
@@ -52131,7 +53271,7 @@
         </is>
       </c>
       <c r="M222" t="n">
-        <v>11.4343</v>
+        <v>2.9568</v>
       </c>
       <c r="N222" t="n">
         <v>-11950.8608</v>
@@ -52263,6 +53403,38 @@
         </is>
       </c>
       <c r="CI222" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CP222" t="n">
+        <v>167642232</v>
+      </c>
+      <c r="CQ222" t="n">
+        <v>100</v>
+      </c>
+      <c r="CR222" t="inlineStr">
+        <is>
+          <t>LONG-TERM BORROWINGS</t>
+        </is>
+      </c>
+      <c r="CS222" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CZ222" t="n">
+        <v>23295907</v>
+      </c>
+      <c r="DA222" t="n">
+        <v>106</v>
+      </c>
+      <c r="DB222" t="inlineStr">
+        <is>
+          <t>Lease liabilities</t>
+        </is>
+      </c>
+      <c r="DC222" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -52324,7 +53496,7 @@
         <v>0</v>
       </c>
       <c r="K223" t="n">
-        <v>948071628</v>
+        <v>738383026</v>
       </c>
       <c r="L223" t="inlineStr">
         <is>
@@ -52332,7 +53504,7 @@
         </is>
       </c>
       <c r="M223" t="n">
-        <v>11.5331</v>
+        <v>8.9823</v>
       </c>
       <c r="N223" t="n">
         <v>-20251.3104</v>
@@ -52461,6 +53633,38 @@
         </is>
       </c>
       <c r="CI223" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CK223" t="n">
+        <v>173589172</v>
+      </c>
+      <c r="CL223" t="n">
+        <v>81</v>
+      </c>
+      <c r="CM223" t="inlineStr">
+        <is>
+          <t>Current Portion of Long-term Loans</t>
+        </is>
+      </c>
+      <c r="CN223" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CP223" t="n">
+        <v>564793854</v>
+      </c>
+      <c r="CQ223" t="n">
+        <v>81</v>
+      </c>
+      <c r="CR223" t="inlineStr">
+        <is>
+          <t>Long-term Loans</t>
+        </is>
+      </c>
+      <c r="CS223" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -52503,7 +53707,7 @@
         <v>0</v>
       </c>
       <c r="J224" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K224" t="n">
         <v>1444</v>
@@ -52658,6 +53862,9 @@
           <t>assumed 100% parent NP (no NCI attribution row found)</t>
         </is>
       </c>
+      <c r="BQ224" t="n">
+        <v>0.032</v>
+      </c>
       <c r="BR224" t="n">
         <v>52</v>
       </c>
@@ -52668,12 +53875,12 @@
       </c>
       <c r="BT224" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="BU224" t="inlineStr">
         <is>
-          <t>label found but no number extracted</t>
+          <t>fils/baisa→BHD: recovered (orig=None, fils=32.000)</t>
         </is>
       </c>
       <c r="DE224" t="n">
@@ -52741,7 +53948,7 @@
         <v>0</v>
       </c>
       <c r="J225" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K225" t="n">
         <v>1374</v>
@@ -52896,6 +54103,9 @@
           <t>assumed 100% parent NP (no NCI attribution row found)</t>
         </is>
       </c>
+      <c r="BQ225" t="n">
+        <v>0.029</v>
+      </c>
       <c r="BR225" t="n">
         <v>118</v>
       </c>
@@ -52906,12 +54116,12 @@
       </c>
       <c r="BT225" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="BU225" t="inlineStr">
         <is>
-          <t>label found but no number extracted</t>
+          <t>fils/baisa→BHD: recovered (orig=None, fils=29.000)</t>
         </is>
       </c>
       <c r="CG225" t="n">
@@ -53002,7 +54212,7 @@
         <v>0</v>
       </c>
       <c r="J226" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K226" t="n">
         <v>1253</v>
@@ -53157,6 +54367,9 @@
           <t>assumed 100% parent NP (no NCI attribution row found)</t>
         </is>
       </c>
+      <c r="BQ226" t="n">
+        <v>0.033</v>
+      </c>
       <c r="BR226" t="n">
         <v>74</v>
       </c>
@@ -53167,12 +54380,12 @@
       </c>
       <c r="BT226" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="BU226" t="inlineStr">
         <is>
-          <t>label found but no number extracted</t>
+          <t>fils/baisa→BHD: recovered (orig=None, fils=33.000)</t>
         </is>
       </c>
       <c r="DE226" t="n">
@@ -53240,7 +54453,7 @@
         <v>0</v>
       </c>
       <c r="J227" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K227" t="n">
         <v>0</v>
@@ -53400,6 +54613,9 @@
           <t>assumed 100% parent NP (no NCI attribution row found)</t>
         </is>
       </c>
+      <c r="BQ227" t="n">
+        <v>0.035</v>
+      </c>
       <c r="BR227" t="n">
         <v>76</v>
       </c>
@@ -53410,12 +54626,12 @@
       </c>
       <c r="BT227" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="BU227" t="inlineStr">
         <is>
-          <t>label found but no number extracted</t>
+          <t>fils/baisa→BHD: recovered (orig=None, fils=35.000)</t>
         </is>
       </c>
       <c r="DF227" t="n">
@@ -53485,7 +54701,7 @@
         <v>0</v>
       </c>
       <c r="J228" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K228" t="n">
         <v>1538</v>
@@ -53646,6 +54862,9 @@
           <t>coordinate extraction</t>
         </is>
       </c>
+      <c r="BQ228" t="n">
+        <v>0.036</v>
+      </c>
       <c r="BR228" t="n">
         <v>71</v>
       </c>
@@ -53656,12 +54875,12 @@
       </c>
       <c r="BT228" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="BU228" t="inlineStr">
         <is>
-          <t>label found but no number extracted</t>
+          <t>fils/baisa→BHD: recovered (orig=None, fils=36.000)</t>
         </is>
       </c>
       <c r="DE228" t="n">
@@ -53729,7 +54948,7 @@
         <v>0</v>
       </c>
       <c r="J229" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L229" t="inlineStr">
         <is>
@@ -53889,6 +55108,9 @@
           <t>assumed 100% parent NP (no NCI attribution row found)</t>
         </is>
       </c>
+      <c r="BQ229" t="n">
+        <v>0.038</v>
+      </c>
       <c r="BR229" t="n">
         <v>72</v>
       </c>
@@ -53899,12 +55121,12 @@
       </c>
       <c r="BT229" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="BU229" t="inlineStr">
         <is>
-          <t>label found but no number extracted</t>
+          <t>fils/baisa→BHD: recovered (orig=None, fils=38.000)</t>
         </is>
       </c>
       <c r="EI229" t="n">
@@ -54109,6 +55331,9 @@
           <t>high</t>
         </is>
       </c>
+      <c r="BQ230" t="n">
+        <v>246341</v>
+      </c>
       <c r="BR230" t="n">
         <v>138</v>
       </c>
@@ -54119,12 +55344,7 @@
       </c>
       <c r="BT230" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="BU230" t="inlineStr">
-        <is>
-          <t>fils/baisa: value 246341 too large; no valid fils found in 20-line context</t>
+          <t>high</t>
         </is>
       </c>
       <c r="DE230" t="n">
@@ -54366,6 +55586,9 @@
           <t>high</t>
         </is>
       </c>
+      <c r="BQ231" t="n">
+        <v>362249</v>
+      </c>
       <c r="BR231" t="n">
         <v>144</v>
       </c>
@@ -54376,12 +55599,7 @@
       </c>
       <c r="BT231" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="BU231" t="inlineStr">
-        <is>
-          <t>fils/baisa: value 362249 too large; no valid fils found in 20-line context</t>
+          <t>high</t>
         </is>
       </c>
       <c r="DE231" t="n">
@@ -54618,6 +55836,9 @@
           <t>high</t>
         </is>
       </c>
+      <c r="BQ232" t="n">
+        <v>509085</v>
+      </c>
       <c r="BR232" t="n">
         <v>144</v>
       </c>
@@ -54628,12 +55849,7 @@
       </c>
       <c r="BT232" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="BU232" t="inlineStr">
-        <is>
-          <t>fils/baisa: value 509085 too large; no valid fils found in 20-line context</t>
+          <t>high</t>
         </is>
       </c>
       <c r="DE232" t="n">
@@ -54859,6 +56075,9 @@
           <t>high</t>
         </is>
       </c>
+      <c r="BQ233" t="n">
+        <v>560620</v>
+      </c>
       <c r="BR233" t="n">
         <v>78</v>
       </c>
@@ -54869,12 +56088,7 @@
       </c>
       <c r="BT233" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="BU233" t="inlineStr">
-        <is>
-          <t>fils/baisa: value 560620 too large; no valid fils found in 20-line context</t>
+          <t>high</t>
         </is>
       </c>
       <c r="DE233" t="n">
@@ -55116,6 +56330,9 @@
           <t>high</t>
         </is>
       </c>
+      <c r="BQ234" t="n">
+        <v>600122</v>
+      </c>
       <c r="BR234" t="n">
         <v>156</v>
       </c>
@@ -55126,12 +56343,7 @@
       </c>
       <c r="BT234" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="BU234" t="inlineStr">
-        <is>
-          <t>fils/baisa: value 600122 too large; no valid fils found in 20-line context</t>
+          <t>high</t>
         </is>
       </c>
       <c r="DE234" t="n">
@@ -55368,6 +56580,9 @@
           <t>high</t>
         </is>
       </c>
+      <c r="BQ235" t="n">
+        <v>575648</v>
+      </c>
       <c r="BR235" t="n">
         <v>178</v>
       </c>
@@ -55378,12 +56593,7 @@
       </c>
       <c r="BT235" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="BU235" t="inlineStr">
-        <is>
-          <t>fils/baisa: value 575648 too large; no valid fils found in 20-line context</t>
+          <t>high</t>
         </is>
       </c>
       <c r="DE235" t="n">
@@ -55935,7 +57145,7 @@
         <v>0</v>
       </c>
       <c r="K238" t="n">
-        <v>4666315</v>
+        <v>5151752</v>
       </c>
       <c r="L238" t="inlineStr">
         <is>
@@ -55943,7 +57153,7 @@
         </is>
       </c>
       <c r="M238" t="n">
-        <v>0.2133</v>
+        <v>0.2355</v>
       </c>
       <c r="N238" t="n">
         <v>0</v>
@@ -56108,14 +57318,14 @@
         </is>
       </c>
       <c r="CP238" t="n">
-        <v>4514563</v>
+        <v>5000000</v>
       </c>
       <c r="CQ238" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="CR238" t="inlineStr">
         <is>
-          <t>Long-term borrowings</t>
+          <t>Long term loans</t>
         </is>
       </c>
       <c r="CS238" t="inlineStr">
@@ -56196,7 +57406,7 @@
         <v>0</v>
       </c>
       <c r="K239" t="n">
-        <v>4449600</v>
+        <v>5148234</v>
       </c>
       <c r="L239" t="inlineStr">
         <is>
@@ -56204,7 +57414,7 @@
         </is>
       </c>
       <c r="M239" t="n">
-        <v>0.1948</v>
+        <v>0.2254</v>
       </c>
       <c r="N239" t="n">
         <v>0</v>
@@ -56390,14 +57600,14 @@
         </is>
       </c>
       <c r="CP239" t="n">
-        <v>4301366</v>
+        <v>5000000</v>
       </c>
       <c r="CQ239" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="CR239" t="inlineStr">
         <is>
-          <t>Long-term borrowings</t>
+          <t>Long term loans</t>
         </is>
       </c>
       <c r="CS239" t="inlineStr">
@@ -58721,7 +59931,7 @@
         <v>0</v>
       </c>
       <c r="K248" t="n">
-        <v>36</v>
+        <v>189</v>
       </c>
       <c r="L248" t="inlineStr">
         <is>
@@ -58783,6 +59993,22 @@
       <c r="CJ248" t="inlineStr">
         <is>
           <t>label found but no number extracted</t>
+        </is>
+      </c>
+      <c r="CP248" t="n">
+        <v>153.58</v>
+      </c>
+      <c r="CQ248" t="n">
+        <v>134</v>
+      </c>
+      <c r="CR248" t="inlineStr">
+        <is>
+          <t>Term loan</t>
+        </is>
+      </c>
+      <c r="CS248" t="inlineStr">
+        <is>
+          <t>high</t>
         </is>
       </c>
       <c r="CU248" t="n">
@@ -58860,7 +60086,7 @@
         <v>0</v>
       </c>
       <c r="K249" t="n">
-        <v>6</v>
+        <v>441</v>
       </c>
       <c r="L249" t="inlineStr">
         <is>
@@ -58923,6 +60149,22 @@
       <c r="CJ249" t="inlineStr">
         <is>
           <t>label found but no number extracted</t>
+        </is>
+      </c>
+      <c r="CP249" t="n">
+        <v>435.225</v>
+      </c>
+      <c r="CQ249" t="n">
+        <v>157</v>
+      </c>
+      <c r="CR249" t="inlineStr">
+        <is>
+          <t>Term loan</t>
+        </is>
+      </c>
+      <c r="CS249" t="inlineStr">
+        <is>
+          <t>high</t>
         </is>
       </c>
       <c r="CU249" t="n">
@@ -61944,10 +63186,16 @@
       <c r="J261" t="b">
         <v>0</v>
       </c>
+      <c r="K261" t="n">
+        <v>150726</v>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="M261" t="n">
+        <v>0.0167</v>
       </c>
       <c r="N261" t="n">
         <v>0.7633</v>
@@ -62131,6 +63379,22 @@
       <c r="BU261" t="inlineStr">
         <is>
           <t>coordinate extraction</t>
+        </is>
+      </c>
+      <c r="CZ261" t="n">
+        <v>150726</v>
+      </c>
+      <c r="DA261" t="n">
+        <v>63</v>
+      </c>
+      <c r="DB261" t="inlineStr">
+        <is>
+          <t>Finance lease liabilities</t>
+        </is>
+      </c>
+      <c r="DC261" t="inlineStr">
+        <is>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -66037,7 +67301,7 @@
         <v>0</v>
       </c>
       <c r="K278" t="n">
-        <v>11664830</v>
+        <v>14648291</v>
       </c>
       <c r="L278" t="inlineStr">
         <is>
@@ -66045,7 +67309,7 @@
         </is>
       </c>
       <c r="M278" t="n">
-        <v>1.8804</v>
+        <v>2.3613</v>
       </c>
       <c r="N278" t="n">
         <v>0.9122</v>
@@ -66187,6 +67451,22 @@
         </is>
       </c>
       <c r="CN278" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CP278" t="n">
+        <v>2983461</v>
+      </c>
+      <c r="CQ278" t="n">
+        <v>65</v>
+      </c>
+      <c r="CR278" t="inlineStr">
+        <is>
+          <t>Long-term loans</t>
+        </is>
+      </c>
+      <c r="CS278" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -66248,7 +67528,7 @@
         <v>0</v>
       </c>
       <c r="K279" t="n">
-        <v>111458</v>
+        <v>10829511</v>
       </c>
       <c r="L279" t="inlineStr">
         <is>
@@ -66256,7 +67536,7 @@
         </is>
       </c>
       <c r="M279" t="n">
-        <v>0.0015</v>
+        <v>0.1476</v>
       </c>
       <c r="N279" t="n">
         <v>0</v>
@@ -66353,6 +67633,54 @@
         </is>
       </c>
       <c r="CI279" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CK279" t="n">
+        <v>5223</v>
+      </c>
+      <c r="CL279" t="n">
+        <v>62</v>
+      </c>
+      <c r="CM279" t="inlineStr">
+        <is>
+          <t>Current portion of long-term loans</t>
+        </is>
+      </c>
+      <c r="CN279" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CP279" t="n">
+        <v>179101</v>
+      </c>
+      <c r="CQ279" t="n">
+        <v>62</v>
+      </c>
+      <c r="CR279" t="inlineStr">
+        <is>
+          <t>Long-term loans</t>
+        </is>
+      </c>
+      <c r="CS279" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CZ279" t="n">
+        <v>10645187</v>
+      </c>
+      <c r="DA279" t="n">
+        <v>62</v>
+      </c>
+      <c r="DB279" t="inlineStr">
+        <is>
+          <t>Lease liabilities</t>
+        </is>
+      </c>
+      <c r="DC279" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -66398,7 +67726,7 @@
         <v>0</v>
       </c>
       <c r="K280" t="n">
-        <v>10108939</v>
+        <v>10344167</v>
       </c>
       <c r="L280" t="inlineStr">
         <is>
@@ -66406,7 +67734,7 @@
         </is>
       </c>
       <c r="M280" t="n">
-        <v>0.1541</v>
+        <v>0.1577</v>
       </c>
       <c r="N280" t="n">
         <v>0</v>
@@ -66503,6 +67831,54 @@
         </is>
       </c>
       <c r="CI280" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CK280" t="n">
+        <v>4151</v>
+      </c>
+      <c r="CL280" t="n">
+        <v>66</v>
+      </c>
+      <c r="CM280" t="inlineStr">
+        <is>
+          <t>Current portion of long-term loans</t>
+        </is>
+      </c>
+      <c r="CN280" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CP280" t="n">
+        <v>244540</v>
+      </c>
+      <c r="CQ280" t="n">
+        <v>66</v>
+      </c>
+      <c r="CR280" t="inlineStr">
+        <is>
+          <t>Long-term loans</t>
+        </is>
+      </c>
+      <c r="CS280" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CZ280" t="n">
+        <v>10095476</v>
+      </c>
+      <c r="DA280" t="n">
+        <v>66</v>
+      </c>
+      <c r="DB280" t="inlineStr">
+        <is>
+          <t>Lease liabilities</t>
+        </is>
+      </c>
+      <c r="DC280" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -66548,7 +67924,7 @@
         <v>0</v>
       </c>
       <c r="K281" t="n">
-        <v>9473423</v>
+        <v>9742169</v>
       </c>
       <c r="L281" t="inlineStr">
         <is>
@@ -66556,7 +67932,7 @@
         </is>
       </c>
       <c r="M281" t="n">
-        <v>0.8979</v>
+        <v>0.9234</v>
       </c>
       <c r="N281" t="n">
         <v>0.8331</v>
@@ -66680,6 +68056,22 @@
         </is>
       </c>
       <c r="CN281" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CP281" t="n">
+        <v>268746</v>
+      </c>
+      <c r="CQ281" t="n">
+        <v>64</v>
+      </c>
+      <c r="CR281" t="inlineStr">
+        <is>
+          <t>Long-term loans</t>
+        </is>
+      </c>
+      <c r="CS281" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -66741,7 +68133,7 @@
         <v>0</v>
       </c>
       <c r="K282" t="n">
-        <v>8837862</v>
+        <v>9120452</v>
       </c>
       <c r="L282" t="inlineStr">
         <is>
@@ -66749,7 +68141,7 @@
         </is>
       </c>
       <c r="M282" t="n">
-        <v>224.6019</v>
+        <v>231.7836</v>
       </c>
       <c r="N282" t="n">
         <v>0.4434</v>
@@ -66881,6 +68273,22 @@
         </is>
       </c>
       <c r="CN282" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CP282" t="n">
+        <v>282590</v>
+      </c>
+      <c r="CQ282" t="n">
+        <v>82</v>
+      </c>
+      <c r="CR282" t="inlineStr">
+        <is>
+          <t>Long-term loans</t>
+        </is>
+      </c>
+      <c r="CS282" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -66958,7 +68366,7 @@
         <v>0</v>
       </c>
       <c r="K283" t="n">
-        <v>16990123</v>
+        <v>8213016</v>
       </c>
       <c r="L283" t="inlineStr">
         <is>
@@ -66966,7 +68374,7 @@
         </is>
       </c>
       <c r="M283" t="n">
-        <v>1303.9235</v>
+        <v>630.3159000000001</v>
       </c>
       <c r="N283" t="n">
         <v>0.7557</v>
@@ -67079,6 +68487,22 @@
         </is>
       </c>
       <c r="CI283" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CZ283" t="n">
+        <v>8213016</v>
+      </c>
+      <c r="DA283" t="n">
+        <v>94</v>
+      </c>
+      <c r="DB283" t="inlineStr">
+        <is>
+          <t>Lease liabilities</t>
+        </is>
+      </c>
+      <c r="DC283" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -67617,10 +69041,16 @@
       <c r="J286" t="b">
         <v>0</v>
       </c>
+      <c r="K286" t="n">
+        <v>0</v>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>zero</t>
+        </is>
+      </c>
+      <c r="M286" t="n">
+        <v>0</v>
       </c>
       <c r="N286" t="n">
         <v>0.8438</v>
@@ -67893,10 +69323,16 @@
       <c r="J287" t="b">
         <v>0</v>
       </c>
+      <c r="K287" t="n">
+        <v>0</v>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>zero</t>
+        </is>
+      </c>
+      <c r="M287" t="n">
+        <v>0</v>
       </c>
       <c r="N287" t="n">
         <v>0.8442</v>
@@ -68464,10 +69900,16 @@
       <c r="J289" t="b">
         <v>0</v>
       </c>
+      <c r="K289" t="n">
+        <v>0</v>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>zero</t>
+        </is>
+      </c>
+      <c r="M289" t="n">
+        <v>0</v>
       </c>
       <c r="N289" t="n">
         <v>0.8547</v>
@@ -69535,7 +70977,7 @@
         <v>0</v>
       </c>
       <c r="K296" t="n">
-        <v>692303</v>
+        <v>6050</v>
       </c>
       <c r="L296" t="inlineStr">
         <is>
@@ -69543,7 +70985,7 @@
         </is>
       </c>
       <c r="M296" t="n">
-        <v>0.0944</v>
+        <v>0.0008</v>
       </c>
       <c r="N296" t="n">
         <v>-581.1955</v>
@@ -69719,6 +71161,38 @@
         </is>
       </c>
       <c r="CI296" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CP296" t="n">
+        <v>5050</v>
+      </c>
+      <c r="CQ296" t="n">
+        <v>72</v>
+      </c>
+      <c r="CR296" t="inlineStr">
+        <is>
+          <t>Long-term loans</t>
+        </is>
+      </c>
+      <c r="CS296" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CU296" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CV296" t="n">
+        <v>72</v>
+      </c>
+      <c r="CW296" t="inlineStr">
+        <is>
+          <t>Islamic Sukuk</t>
+        </is>
+      </c>
+      <c r="CX296" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -69780,7 +71254,7 @@
         <v>0</v>
       </c>
       <c r="K297" t="n">
-        <v>5863402</v>
+        <v>5933402</v>
       </c>
       <c r="L297" t="inlineStr">
         <is>
@@ -69788,7 +71262,7 @@
         </is>
       </c>
       <c r="M297" t="n">
-        <v>0.402</v>
+        <v>0.4068</v>
       </c>
       <c r="N297" t="n">
         <v>0.3595</v>
@@ -69954,6 +71428,22 @@
         </is>
       </c>
       <c r="CI297" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CK297" t="n">
+        <v>70000</v>
+      </c>
+      <c r="CL297" t="n">
+        <v>83</v>
+      </c>
+      <c r="CM297" t="inlineStr">
+        <is>
+          <t>Short term loan</t>
+        </is>
+      </c>
+      <c r="CN297" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -73255,10 +74745,16 @@
       <c r="J314" t="b">
         <v>0</v>
       </c>
+      <c r="K314" t="n">
+        <v>0</v>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>zero</t>
+        </is>
+      </c>
+      <c r="M314" t="n">
+        <v>0</v>
       </c>
       <c r="N314" t="n">
         <v>0.9978</v>
@@ -73565,10 +75061,16 @@
       <c r="J319" t="b">
         <v>0</v>
       </c>
+      <c r="K319" t="n">
+        <v>0</v>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>zero</t>
+        </is>
+      </c>
+      <c r="M319" t="n">
+        <v>0</v>
       </c>
       <c r="N319" t="n">
         <v>0.1736</v>
@@ -74322,7 +75824,7 @@
         <v>0</v>
       </c>
       <c r="K322" t="n">
-        <v>30691</v>
+        <v>31985</v>
       </c>
       <c r="L322" t="inlineStr">
         <is>
@@ -74330,7 +75832,7 @@
         </is>
       </c>
       <c r="M322" t="n">
-        <v>0.0185</v>
+        <v>0.0193</v>
       </c>
       <c r="N322" t="n">
         <v>0.3316</v>
@@ -74524,6 +76026,22 @@
         </is>
       </c>
       <c r="CN322" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CP322" t="n">
+        <v>1294</v>
+      </c>
+      <c r="CQ322" t="n">
+        <v>126</v>
+      </c>
+      <c r="CR322" t="inlineStr">
+        <is>
+          <t>Islamic financing</t>
+        </is>
+      </c>
+      <c r="CS322" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -76261,10 +77779,16 @@
       <c r="J332" t="b">
         <v>0</v>
       </c>
+      <c r="K332" t="n">
+        <v>0</v>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>zero</t>
+        </is>
+      </c>
+      <c r="M332" t="n">
+        <v>0</v>
       </c>
       <c r="N332" t="n">
         <v>-8.9071</v>
@@ -76565,10 +78089,16 @@
       <c r="J335" t="b">
         <v>0</v>
       </c>
+      <c r="K335" t="n">
+        <v>0</v>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>zero</t>
+        </is>
+      </c>
+      <c r="M335" t="n">
+        <v>0</v>
       </c>
       <c r="N335" t="n">
         <v>0.06950000000000001</v>
@@ -76752,10 +78282,16 @@
       <c r="J336" t="b">
         <v>0</v>
       </c>
+      <c r="K336" t="n">
+        <v>0</v>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>zero</t>
+        </is>
+      </c>
+      <c r="M336" t="n">
+        <v>0</v>
       </c>
       <c r="N336" t="n">
         <v>0.0263</v>
@@ -76988,7 +78524,7 @@
         <v>0</v>
       </c>
       <c r="K338" t="n">
-        <v>2989350</v>
+        <v>15927794</v>
       </c>
       <c r="L338" t="inlineStr">
         <is>
@@ -76996,7 +78532,7 @@
         </is>
       </c>
       <c r="M338" t="n">
-        <v>0.0393</v>
+        <v>0.2093</v>
       </c>
       <c r="N338" t="n">
         <v>-5520.598</v>
@@ -77182,14 +78718,14 @@
         </is>
       </c>
       <c r="CP338" t="n">
-        <v>2237853</v>
+        <v>15176297</v>
       </c>
       <c r="CQ338" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="CR338" t="inlineStr">
         <is>
-          <t>Long term borrowings</t>
+          <t>Long term loans</t>
         </is>
       </c>
       <c r="CS338" t="inlineStr">
@@ -77270,7 +78806,7 @@
         <v>0</v>
       </c>
       <c r="K339" t="n">
-        <v>8962763</v>
+        <v>4331138</v>
       </c>
       <c r="L339" t="inlineStr">
         <is>
@@ -77278,7 +78814,7 @@
         </is>
       </c>
       <c r="M339" t="n">
-        <v>0.1426</v>
+        <v>0.0689</v>
       </c>
       <c r="N339" t="n">
         <v>0.4119</v>
@@ -77459,14 +78995,14 @@
         </is>
       </c>
       <c r="CP339" t="n">
-        <v>8637605</v>
+        <v>4005980</v>
       </c>
       <c r="CQ339" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="CR339" t="inlineStr">
         <is>
-          <t>Long term borrowings</t>
+          <t>Long term loans</t>
         </is>
       </c>
       <c r="CS339" t="inlineStr">
@@ -77547,7 +79083,7 @@
         <v>0</v>
       </c>
       <c r="K340" t="n">
-        <v>9309965</v>
+        <v>5428838</v>
       </c>
       <c r="L340" t="inlineStr">
         <is>
@@ -77555,7 +79091,7 @@
         </is>
       </c>
       <c r="M340" t="n">
-        <v>0.1675</v>
+        <v>0.0977</v>
       </c>
       <c r="N340" t="n">
         <v>-520.6944999999999</v>
@@ -77736,14 +79272,14 @@
         </is>
       </c>
       <c r="CP340" t="n">
-        <v>7846606</v>
+        <v>3965479</v>
       </c>
       <c r="CQ340" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="CR340" t="inlineStr">
         <is>
-          <t>Long-term borrowings</t>
+          <t>Long-term loans</t>
         </is>
       </c>
       <c r="CS340" t="inlineStr">
@@ -77824,7 +79360,7 @@
         <v>0</v>
       </c>
       <c r="K341" t="n">
-        <v>6677</v>
+        <v>8930153</v>
       </c>
       <c r="L341" t="inlineStr">
         <is>
@@ -77832,7 +79368,7 @@
         </is>
       </c>
       <c r="M341" t="n">
-        <v>0.0001</v>
+        <v>0.1446</v>
       </c>
       <c r="N341" t="n">
         <v>0.4671</v>
@@ -77987,6 +79523,22 @@
         </is>
       </c>
       <c r="CI341" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CP341" t="n">
+        <v>8923476</v>
+      </c>
+      <c r="CQ341" t="n">
+        <v>68</v>
+      </c>
+      <c r="CR341" t="inlineStr">
+        <is>
+          <t>Long-term loans</t>
+        </is>
+      </c>
+      <c r="CS341" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -78064,7 +79616,7 @@
         <v>0</v>
       </c>
       <c r="K342" t="n">
-        <v>4679</v>
+        <v>8642284</v>
       </c>
       <c r="L342" t="inlineStr">
         <is>
@@ -78072,7 +79624,7 @@
         </is>
       </c>
       <c r="M342" t="n">
-        <v>0.0001</v>
+        <v>0.1352</v>
       </c>
       <c r="N342" t="n">
         <v>0.4649</v>
@@ -78227,6 +79779,22 @@
         </is>
       </c>
       <c r="CI342" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CP342" t="n">
+        <v>8637605</v>
+      </c>
+      <c r="CQ342" t="n">
+        <v>74</v>
+      </c>
+      <c r="CR342" t="inlineStr">
+        <is>
+          <t>Long-term loans</t>
+        </is>
+      </c>
+      <c r="CS342" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -78304,7 +79872,7 @@
         <v>0</v>
       </c>
       <c r="K343" t="n">
-        <v>4680</v>
+        <v>7851286</v>
       </c>
       <c r="L343" t="inlineStr">
         <is>
@@ -78312,7 +79880,7 @@
         </is>
       </c>
       <c r="M343" t="n">
-        <v>0.0001</v>
+        <v>0.1133</v>
       </c>
       <c r="N343" t="n">
         <v>0.4413</v>
@@ -78467,6 +80035,22 @@
         </is>
       </c>
       <c r="CI343" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CP343" t="n">
+        <v>7846606</v>
+      </c>
+      <c r="CQ343" t="n">
+        <v>84</v>
+      </c>
+      <c r="CR343" t="inlineStr">
+        <is>
+          <t>Long-term loans</t>
+        </is>
+      </c>
+      <c r="CS343" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -80972,7 +82556,7 @@
         <v>0</v>
       </c>
       <c r="K354" t="n">
-        <v>570313</v>
+        <v>32036</v>
       </c>
       <c r="L354" t="inlineStr">
         <is>
@@ -80980,7 +82564,7 @@
         </is>
       </c>
       <c r="M354" t="n">
-        <v>0.2444</v>
+        <v>0.0137</v>
       </c>
       <c r="N354" t="n">
         <v>-315.9762</v>
@@ -81163,6 +82747,22 @@
         </is>
       </c>
       <c r="CI354" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="DE354" t="n">
+        <v>32036</v>
+      </c>
+      <c r="DF354" t="n">
+        <v>50</v>
+      </c>
+      <c r="DG354" t="inlineStr">
+        <is>
+          <t>Due to banks</t>
+        </is>
+      </c>
+      <c r="DH354" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -81524,7 +83124,7 @@
         <v>0</v>
       </c>
       <c r="K356" t="n">
-        <v>82383200</v>
+        <v>82430000</v>
       </c>
       <c r="L356" t="inlineStr">
         <is>
@@ -81532,7 +83132,7 @@
         </is>
       </c>
       <c r="M356" t="n">
-        <v>4.7991</v>
+        <v>4.8019</v>
       </c>
       <c r="N356" t="n">
         <v>-0.7151999999999999</v>
@@ -81717,6 +83317,22 @@
         </is>
       </c>
       <c r="CI356" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CP356" t="n">
+        <v>82430000</v>
+      </c>
+      <c r="CQ356" t="n">
+        <v>52</v>
+      </c>
+      <c r="CR356" t="inlineStr">
+        <is>
+          <t>Term loans</t>
+        </is>
+      </c>
+      <c r="CS356" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -81980,6 +83596,27 @@
           <t>coordinate extraction</t>
         </is>
       </c>
+      <c r="CK357" t="n">
+        <v>82290000</v>
+      </c>
+      <c r="CL357" t="n">
+        <v>28</v>
+      </c>
+      <c r="CM357" t="inlineStr">
+        <is>
+          <t>Bank facilities</t>
+        </is>
+      </c>
+      <c r="CN357" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CO357" t="inlineStr">
+        <is>
+          <t>coordinate extraction</t>
+        </is>
+      </c>
       <c r="EI357" t="n">
         <v>1997</v>
       </c>
@@ -82036,10 +83673,16 @@
       <c r="J358" t="b">
         <v>0</v>
       </c>
+      <c r="K358" t="n">
+        <v>13540000</v>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="M358" t="n">
+        <v>0.7861</v>
       </c>
       <c r="N358" t="n">
         <v>0.9314</v>
@@ -82205,6 +83848,27 @@
       <c r="BK358" t="inlineStr">
         <is>
           <t>assumed 100% parent NP (no NCI attribution row found)</t>
+        </is>
+      </c>
+      <c r="CK358" t="n">
+        <v>13540000</v>
+      </c>
+      <c r="CL358" t="n">
+        <v>30</v>
+      </c>
+      <c r="CM358" t="inlineStr">
+        <is>
+          <t>Bank facilities</t>
+        </is>
+      </c>
+      <c r="CN358" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CO358" t="inlineStr">
+        <is>
+          <t>coordinate extraction</t>
         </is>
       </c>
       <c r="EI358" t="n">
@@ -82263,10 +83927,16 @@
       <c r="J359" t="b">
         <v>0</v>
       </c>
+      <c r="K359" t="n">
+        <v>11500000</v>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="M359" t="n">
+        <v>0.6665</v>
       </c>
       <c r="N359" t="n">
         <v>0.9578</v>
@@ -82427,6 +84097,27 @@
       <c r="BK359" t="inlineStr">
         <is>
           <t>assumed 100% parent NP (no NCI attribution row found)</t>
+        </is>
+      </c>
+      <c r="CK359" t="n">
+        <v>11500000</v>
+      </c>
+      <c r="CL359" t="n">
+        <v>28</v>
+      </c>
+      <c r="CM359" t="inlineStr">
+        <is>
+          <t>Bank facilities</t>
+        </is>
+      </c>
+      <c r="CN359" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CO359" t="inlineStr">
+        <is>
+          <t>coordinate extraction</t>
         </is>
       </c>
       <c r="EI359" t="n">
@@ -82485,10 +84176,16 @@
       <c r="J360" t="b">
         <v>0</v>
       </c>
+      <c r="K360" t="n">
+        <v>4974965</v>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="M360" t="n">
+        <v>0.2882</v>
       </c>
       <c r="N360" t="n">
         <v>0.9887</v>
@@ -82654,6 +84351,27 @@
       <c r="BK360" t="inlineStr">
         <is>
           <t>assumed 100% parent NP (no NCI attribution row found)</t>
+        </is>
+      </c>
+      <c r="CK360" t="n">
+        <v>4974965</v>
+      </c>
+      <c r="CL360" t="n">
+        <v>28</v>
+      </c>
+      <c r="CM360" t="inlineStr">
+        <is>
+          <t>Bank facilities</t>
+        </is>
+      </c>
+      <c r="CN360" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CO360" t="inlineStr">
+        <is>
+          <t>coordinate extraction</t>
         </is>
       </c>
       <c r="EI360" t="n">
@@ -82712,10 +84430,16 @@
       <c r="J361" t="b">
         <v>0</v>
       </c>
+      <c r="K361" t="n">
+        <v>30988870</v>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="M361" t="n">
+        <v>1.7713</v>
       </c>
       <c r="N361" t="n">
         <v>0.9827</v>
@@ -82876,6 +84600,27 @@
       <c r="BK361" t="inlineStr">
         <is>
           <t>assumed 100% parent NP (no NCI attribution row found)</t>
+        </is>
+      </c>
+      <c r="CK361" t="n">
+        <v>30988870</v>
+      </c>
+      <c r="CL361" t="n">
+        <v>28</v>
+      </c>
+      <c r="CM361" t="inlineStr">
+        <is>
+          <t>Bank facilities</t>
+        </is>
+      </c>
+      <c r="CN361" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CO361" t="inlineStr">
+        <is>
+          <t>coordinate extraction</t>
         </is>
       </c>
       <c r="EI361" t="n">
@@ -85424,10 +87169,16 @@
       <c r="J372" t="b">
         <v>0</v>
       </c>
+      <c r="K372" t="n">
+        <v>131945753</v>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="M372" t="n">
+        <v>0.6852</v>
       </c>
       <c r="N372" t="n">
         <v>0.825</v>
@@ -85621,6 +87372,38 @@
         </is>
       </c>
       <c r="BY372" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="DE372" t="n">
+        <v>85323340</v>
+      </c>
+      <c r="DF372" t="n">
+        <v>91</v>
+      </c>
+      <c r="DG372" t="inlineStr">
+        <is>
+          <t>Money market deposits</t>
+        </is>
+      </c>
+      <c r="DH372" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="DJ372" t="n">
+        <v>46622413</v>
+      </c>
+      <c r="DK372" t="n">
+        <v>91</v>
+      </c>
+      <c r="DL372" t="inlineStr">
+        <is>
+          <t>Debt securities issued</t>
+        </is>
+      </c>
+      <c r="DM372" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -85681,10 +87464,16 @@
       <c r="J373" t="b">
         <v>0</v>
       </c>
+      <c r="K373" t="n">
+        <v>155368560</v>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="M373" t="n">
+        <v>0.7643</v>
       </c>
       <c r="N373" t="n">
         <v>0.8316</v>
@@ -85878,6 +87667,59 @@
         </is>
       </c>
       <c r="BY373" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CF373" t="n">
+        <v>344770227</v>
+      </c>
+      <c r="CG373" t="n">
+        <v>81</v>
+      </c>
+      <c r="CH373" t="inlineStr">
+        <is>
+          <t>Total financing</t>
+        </is>
+      </c>
+      <c r="CI373" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CJ373" t="inlineStr">
+        <is>
+          <t>coordinate extraction</t>
+        </is>
+      </c>
+      <c r="DE373" t="n">
+        <v>82374946</v>
+      </c>
+      <c r="DF373" t="n">
+        <v>88</v>
+      </c>
+      <c r="DG373" t="inlineStr">
+        <is>
+          <t>Money market deposits</t>
+        </is>
+      </c>
+      <c r="DH373" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="DJ373" t="n">
+        <v>72993614</v>
+      </c>
+      <c r="DK373" t="n">
+        <v>88</v>
+      </c>
+      <c r="DL373" t="inlineStr">
+        <is>
+          <t>Debt securities issued</t>
+        </is>
+      </c>
+      <c r="DM373" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -87324,10 +89166,10 @@
         <v>0</v>
       </c>
       <c r="J386" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K386" t="n">
-        <v>214956</v>
+        <v>777829</v>
       </c>
       <c r="L386" t="inlineStr">
         <is>
@@ -87335,7 +89177,7 @@
         </is>
       </c>
       <c r="M386" t="n">
-        <v>0.1634</v>
+        <v>0.5913</v>
       </c>
       <c r="N386" t="n">
         <v>0.6061</v>
@@ -87483,6 +89325,9 @@
           <t>high</t>
         </is>
       </c>
+      <c r="BQ386" t="n">
+        <v>0.766</v>
+      </c>
       <c r="BR386" t="n">
         <v>99</v>
       </c>
@@ -87493,12 +89338,12 @@
       </c>
       <c r="BT386" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="BU386" t="inlineStr">
         <is>
-          <t>fils/baisa: value 185150 too large; no valid fils found in 20-line context</t>
+          <t>fils/baisa→KWD: recovered (orig=185150, fils=766.000)</t>
         </is>
       </c>
       <c r="CK386" t="n">
@@ -87513,6 +89358,22 @@
         </is>
       </c>
       <c r="CN386" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CP386" t="n">
+        <v>562873</v>
+      </c>
+      <c r="CQ386" t="n">
+        <v>96</v>
+      </c>
+      <c r="CR386" t="inlineStr">
+        <is>
+          <t>Long term loans</t>
+        </is>
+      </c>
+      <c r="CS386" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -87587,10 +89448,10 @@
         <v>0</v>
       </c>
       <c r="J387" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K387" t="n">
-        <v>439816</v>
+        <v>937876</v>
       </c>
       <c r="L387" t="inlineStr">
         <is>
@@ -87598,7 +89459,7 @@
         </is>
       </c>
       <c r="M387" t="n">
-        <v>0.3698</v>
+        <v>0.7885</v>
       </c>
       <c r="N387" t="n">
         <v>0.6224</v>
@@ -87746,6 +89607,9 @@
           <t>high</t>
         </is>
       </c>
+      <c r="BQ387" t="n">
+        <v>0.169</v>
+      </c>
       <c r="BR387" t="n">
         <v>94</v>
       </c>
@@ -87756,12 +89620,12 @@
       </c>
       <c r="BT387" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="BU387" t="inlineStr">
         <is>
-          <t>fils/baisa: value 171856 too large; no valid fils found in 20-line context</t>
+          <t>fils/baisa→KWD: recovered (orig=171856, fils=169.000)</t>
         </is>
       </c>
       <c r="CK387" t="n">
@@ -87776,6 +89640,22 @@
         </is>
       </c>
       <c r="CN387" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CP387" t="n">
+        <v>498060</v>
+      </c>
+      <c r="CQ387" t="n">
+        <v>90</v>
+      </c>
+      <c r="CR387" t="inlineStr">
+        <is>
+          <t>Long term loans</t>
+        </is>
+      </c>
+      <c r="CS387" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -87853,7 +89733,7 @@
         <v>0</v>
       </c>
       <c r="K388" t="n">
-        <v>232983</v>
+        <v>771837</v>
       </c>
       <c r="L388" t="inlineStr">
         <is>
@@ -87861,7 +89741,7 @@
         </is>
       </c>
       <c r="M388" t="n">
-        <v>0.1894</v>
+        <v>0.6276</v>
       </c>
       <c r="N388" t="n">
         <v>0.617</v>
@@ -88024,7 +89904,7 @@
       </c>
       <c r="BU388" t="inlineStr">
         <is>
-          <t>fils/baisa: value 195972 too large; no valid fils found in 20-line context</t>
+          <t>fils/baisa: value 195972; no valid fils found in context</t>
         </is>
       </c>
       <c r="CK388" t="n">
@@ -88039,6 +89919,22 @@
         </is>
       </c>
       <c r="CN388" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CP388" t="n">
+        <v>538854</v>
+      </c>
+      <c r="CQ388" t="n">
+        <v>90</v>
+      </c>
+      <c r="CR388" t="inlineStr">
+        <is>
+          <t>Long term loans</t>
+        </is>
+      </c>
+      <c r="CS388" t="inlineStr">
         <is>
           <t>high</t>
         </is>
@@ -88116,7 +90012,7 @@
         <v>0</v>
       </c>
       <c r="K389" t="n">
-        <v>198743</v>
+        <v>761106</v>
       </c>
       <c r="L389" t="inlineStr">
         <is>
@@ -88124,7 +90020,7 @@
         </is>
       </c>
       <c r="M389" t="n">
-        <v>0.1595</v>
+        <v>0.6109</v>
       </c>
       <c r="N389" t="n">
         <v>0.6076</v>
@@ -88299,6 +90195,22 @@
         </is>
       </c>
       <c r="CN389" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="CP389" t="n">
+        <v>562363</v>
+      </c>
+      <c r="CQ389" t="n">
+        <v>87</v>
+      </c>
+      <c r="CR389" t="inlineStr">
+        <is>
+          <t>Long term loans</t>
+        </is>
+      </c>
+      <c r="CS389" t="inlineStr">
         <is>
           <t>high</t>
         </is>
